--- a/Order_To_Cash/04_KPI_Catalogue.xlsx
+++ b/Order_To_Cash/04_KPI_Catalogue.xlsx
@@ -12,9 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blocked KPIs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'KPI Catalogue'!$A$1:$I$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'KPI Catalogue'!$A$1:$I$136</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'KPI Catalogue'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blocked KPIs'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blocked KPIs'!$A$1:$F$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Blocked KPIs'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -168,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -246,19 +246,22 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -646,7 +649,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>131 measures buildable today. Counts are live formulas over the KPI Catalogue tab.</t>
+          <t>135 measures buildable today. Counts are live formulas over the KPI Catalogue tab.</t>
         </is>
       </c>
     </row>
@@ -684,15 +687,15 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A5)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A5,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A5,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A5,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A5,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -708,15 +711,15 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A6)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A6,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A6,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A6,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A6,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -732,15 +735,15 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A7)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A7,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A7,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A7,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A7,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -756,15 +759,15 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A8)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A8,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A8,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A8,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A8,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -780,15 +783,15 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A9)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A9,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A9,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D9" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A9,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A9,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -804,15 +807,15 @@
         </is>
       </c>
       <c r="B10" s="6">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A10)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A10,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A10,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A10,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A10,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -828,15 +831,15 @@
         </is>
       </c>
       <c r="B11" s="4">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A11)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A11,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A11,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D11" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A11,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A11,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -852,15 +855,15 @@
         </is>
       </c>
       <c r="B12" s="6">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A12)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A12,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A12,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A12,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A12,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -876,15 +879,15 @@
         </is>
       </c>
       <c r="B13" s="4">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A13)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A13,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A13,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D13" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A13,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A13,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -900,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A14)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A14,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A14,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A14,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A14,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -924,15 +927,15 @@
         </is>
       </c>
       <c r="B15" s="4">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A15)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A15,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A15,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D15" s="4">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A15,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A15,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -948,15 +951,15 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTIF('KPI Catalogue'!$B$2:$B$132,$A16)</f>
+        <f>COUNTIF('KPI Catalogue'!$B$2:$B$136,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A16,'KPI Catalogue'!$G$2:$G$132,"Core")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A16,'KPI Catalogue'!$G$2:$G$136,"Core")</f>
         <v/>
       </c>
       <c r="D16" s="6">
-        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$132,$A16,'KPI Catalogue'!$G$2:$G$132,"Standard")</f>
+        <f>COUNTIFS('KPI Catalogue'!$B$2:$B$136,$A16,'KPI Catalogue'!$G$2:$G$136,"Standard")</f>
         <v/>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -999,7 +1002,7 @@
         </is>
       </c>
       <c r="B20" s="6">
-        <f>COUNTIF('Blocked KPIs'!$F$2:$F$14,LEFT($A20,SEARCH(" ",$A20)-1))</f>
+        <f>COUNTIF('Blocked KPIs'!$F$2:$F$15,LEFT($A20,SEARCH(" ",$A20)-1))</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1013,7 @@
         </is>
       </c>
       <c r="B21" s="6">
-        <f>COUNTIF('Blocked KPIs'!$F$2:$F$14,LEFT($A21,SEARCH(" ",$A21)-1))</f>
+        <f>COUNTIF('Blocked KPIs'!$F$2:$F$15,LEFT($A21,SEARCH(" ",$A21)-1))</f>
         <v/>
       </c>
     </row>
@@ -1021,7 +1024,7 @@
         </is>
       </c>
       <c r="B22" s="6">
-        <f>COUNTIF('Blocked KPIs'!$F$2:$F$14,LEFT($A22,SEARCH(" ",$A22)-1))</f>
+        <f>COUNTIF('Blocked KPIs'!$F$2:$F$15,LEFT($A22,SEARCH(" ",$A22)-1))</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1035,7 @@
         </is>
       </c>
       <c r="B23" s="6">
-        <f>COUNTIF('Blocked KPIs'!$F$2:$F$14,LEFT($A23,SEARCH(" ",$A23)-1))</f>
+        <f>COUNTIF('Blocked KPIs'!$F$2:$F$15,LEFT($A23,SEARCH(" ",$A23)-1))</f>
         <v/>
       </c>
     </row>
@@ -1048,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1340,7 +1343,7 @@
       </c>
       <c r="I6" s="18" t="inlineStr">
         <is>
-          <t>25,145,676</t>
+          <t>25,346,201</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1437,7 @@
       </c>
       <c r="I8" s="18" t="inlineStr">
         <is>
-          <t>20,335,768</t>
+          <t>20,350,225</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1531,7 @@
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>68,469</t>
+          <t>68,977</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1750,7 @@
       </c>
       <c r="I15" s="25" t="inlineStr">
         <is>
-          <t>60,212</t>
+          <t>60,685</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1772,12 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>USD price converted at the Corporate rate struck on the shipment date.</t>
+          <t>USD price computed from the three-tier rate hierarchy rather than supplied by the source.</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>CALCULATE(COUNTROWS(fact_SalesOrder), fact_SalesOrder[Price_USD_Quality] = "2 - Converted at Corporate rate")</t>
+          <t>CALCULATE(COUNTROWS(fact_SalesOrder), fact_SalesOrder[Price_USD_Quality] = "2 - Converted")</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -1794,7 +1797,7 @@
       </c>
       <c r="I16" s="18" t="inlineStr">
         <is>
-          <t>8,256</t>
+          <t>8,292</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1819,7 @@
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>No usable USD price. One line in the current extract — it carries no local price to convert.</t>
+          <t>No usable USD price. Zero on the v2 extract — kept as a guard.</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -1841,7 +1844,7 @@
       </c>
       <c r="I17" s="25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1866,7 @@
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>Should read 99.999%. Put it on any page showing an average price.</t>
+          <t>Should read 100.000%. Put it on any page showing an average price.</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
@@ -1892,7 +1895,7 @@
       </c>
       <c r="I18" s="18" t="inlineStr">
         <is>
-          <t>99.999%</t>
+          <t>100.000%</t>
         </is>
       </c>
     </row>
@@ -2165,18 +2168,18 @@
       <c r="E24" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
-VAR Currencies    = [Currencies in Context]
 VAR Unconvertible = [Price Unconvertible Lines]
 VAR Coverage      = [Price Coverage %]
+VAR Forward       = [Forward Rate Lines]
 RETURN
     SWITCH(
         TRUE(),
         Unconvertible &gt; 0,
             "! " &amp; FORMAT(Unconvertible, "#,0") &amp; " lines have no USD price and are excluded",
-        Coverage &lt; 0.99,
+        Coverage &lt; 1,
             "! Only " &amp; FORMAT(Coverage, "0.000%") &amp; " of lines have a usable USD price",
-        Currencies &gt; 1 &amp;&amp; [Price Converted Lines] &gt; 0,
-            "i " &amp; FORMAT([Price Converted Lines], "#,0") &amp; " lines converted at the Corporate rate",
+        Forward &gt; 0,
+            "i " &amp; FORMAT(Forward, "#,0") &amp; " lines valued at a carried-forward rate",
         BLANK()
     )</t>
         </is>
@@ -2225,7 +2228,7 @@
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>CALCULATE(COUNTROWS(fact_SalesOrder), fact_SalesOrder[FX_Date_Basis] = "1 - Actual shipment")</t>
+          <t>CALCULATE(COUNTROWS(fact_SalesOrder), fact_SalesOrder[FX_Date_Basis] = "2 - Actual shipment")</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -2245,11 +2248,11 @@
       </c>
       <c r="I25" s="25" t="inlineStr">
         <is>
-          <t>58,906</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="92" customHeight="1">
+          <t>30,617</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="102.5" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
           <t>K-025</t>
@@ -2276,7 +2279,8 @@
 DIVIDE(
     CALCULATE(
         COUNTROWS(fact_SalesOrder),
-        NOT fact_SalesOrder[FX_Date_Basis] IN {"1 - Actual shipment", "2 - Fulfilment"}
+        NOT fact_SalesOrder[FX_Date_Basis] IN {
+            "1 - Source Exchange_Date", "2 - Actual shipment", "3 - Fulfilment" }
     ),
     COUNTROWS(fact_SalesOrder)
 )</t>
@@ -2299,7 +2303,7 @@
       </c>
       <c r="I26" s="18" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2350,7 @@
       </c>
       <c r="I27" s="25" t="inlineStr">
         <is>
-          <t>2,960</t>
+          <t>2,976</t>
         </is>
       </c>
     </row>
@@ -2363,17 +2367,17 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Lines Priced at Promise Date</t>
+          <t>Lines at Source Rate</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Open lines converted at the rate for the date promised to the customer. The forward-looking backlog basis.</t>
+          <t>Rows using the rate the source itself supplied. It reproduces the USD price exactly.</t>
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>CALCULATE(COUNTROWS(fact_SalesOrder), fact_SalesOrder[FX_Date_Basis] = "3 - Promise date (forward)")</t>
+          <t>CALCULATE(COUNTROWS(fact_SalesOrder), fact_SalesOrder[FX_Rate_Source] = "Source Exchange_Rate")</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -2393,7 +2397,7 @@
       </c>
       <c r="I28" s="18" t="inlineStr">
         <is>
-          <t>4,622</t>
+          <t>30,541</t>
         </is>
       </c>
     </row>
@@ -2410,62 +2414,250 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
+          <t>Lines at Table Rate</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>Rows converted by looking the rate up in d_exchange_rate. The only tier that can be forward.</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>CALCULATE(COUNTROWS(fact_SalesOrder), fact_SalesOrder[FX_Rate_Source] = "Corporate rate table")</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>fact_SalesOrder</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I29" s="25" t="inlineStr">
+        <is>
+          <t>5,316</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>K-029</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>02 Currency</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Lines at Identity Rate</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>USD and USC rows. No conversion applied.</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>CALCULATE(COUNTROWS(fact_SalesOrder), fact_SalesOrder[FX_Rate_Source] = "Identity (USD/USC)")</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>fact_SalesOrder</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="inlineStr">
+        <is>
+          <t>33,120</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>K-030</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>11 Data Quality</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>Unresolved Rate Lines</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>Must be zero. Anything here means a currency-region pair is missing from d_exchange_rate.</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>CALCULATE(COUNTROWS(fact_SalesOrder), fact_SalesOrder[FX_Rate_Source] = "Unresolved")</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I31" s="25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>K-031</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>02 Currency</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Lines Priced at Promise Date</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Open lines converted at the rate for the date promised to the customer. The forward-looking backlog basis.</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>CALCULATE(COUNTROWS(fact_SalesOrder), fact_SalesOrder[FX_Date_Basis] = "4 - Promise date (forward)")</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>fact_SalesOrder</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>3,168</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>K-032</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>02 Currency</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
           <t>Forward Rate Lines</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>Rows whose FX date sits beyond the last quoted rate, so the last known rate is carried forward.</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>CALCULATE(COUNTROWS(fact_SalesOrder), fact_SalesOrder[FX_Rate_Is_Forward] = TRUE())</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>fact_SalesOrder</t>
         </is>
       </c>
-      <c r="G29" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>#,0</t>
         </is>
       </c>
-      <c r="I29" s="25" t="inlineStr">
-        <is>
-          <t>1,646</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60.5" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>K-029</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="I33" s="25" t="inlineStr">
+        <is>
+          <t>1,364</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60.5" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>K-033</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>02 Currency</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>Forward Rate Exposure %</t>
         </is>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>How much of the model rests on a carried-forward rate rather than a quoted one.</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
 DIVIDE(
@@ -2474,49 +2666,49 @@
 )</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>fact_SalesOrder</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="I30" s="18" t="inlineStr">
-        <is>
-          <t>2.40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60.5" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>K-030</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="I34" s="18" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60.5" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>K-034</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>02 Currency</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>Backlog MT at Forward Rate</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>Open volume valued at a carried-forward rate. Re-values when d_exchange_rate is refreshed.</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">
 CALCULATE(
@@ -2525,49 +2717,49 @@
 )</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>fact_SalesOrder</t>
         </is>
       </c>
-      <c r="G31" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H31" s="20" t="inlineStr">
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>#,0</t>
         </is>
       </c>
-      <c r="I31" s="25" t="inlineStr">
-        <is>
-          <t>2,752,208</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60.5" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>K-031</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="I35" s="25" t="inlineStr">
+        <is>
+          <t>~2.4m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60.5" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>K-035</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>06 Order to Cash</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>Backlog Value USD</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>Open order book valued in USD. Unshipped lines convert at their promise-date rate, so this is a forward estimate.</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">
 SUMX(
@@ -2576,49 +2768,49 @@
 )</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>\$#,0</t>
         </is>
       </c>
-      <c r="I32" s="18" t="inlineStr">
+      <c r="I36" s="18" t="inlineStr">
         <is>
           <t>forward estimate</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="102.5" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>K-032</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
+    <row r="37" ht="102.5" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>K-036</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>02 Currency</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>Backlog Value Status</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>Put this beside any backlog value so a forward estimate is never read as a settled figure.</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">
 VAR Fwd = [Forward Rate Exposure %]
@@ -2631,139 +2823,139 @@
     )</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>fact_SalesOrder</t>
         </is>
       </c>
-      <c r="G33" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H33" s="20" t="inlineStr">
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I33" s="25" t="inlineStr">
+      <c r="I37" s="25" t="inlineStr">
         <is>
           <t>caption</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>K-033</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>K-037</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>03 Commercial</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>Realised Price per MT</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>Net revenue per tonne billed. The cleanest commercial measure in the model.</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>DIVIDE([Net Revenue USD], [Invoiced MT])</t>
         </is>
       </c>
-      <c r="F34" s="13" t="inlineStr">
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>\$#,0.00</t>
         </is>
       </c>
-      <c r="I34" s="18" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>$676.40</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>K-034</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>K-038</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>03 Commercial</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>Revenue per Order Line</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr"/>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr"/>
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>DIVIDE([Net Revenue USD], [Order Lines])</t>
         </is>
       </c>
-      <c r="F35" s="20" t="inlineStr">
+      <c r="F39" s="20" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G35" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H35" s="20" t="inlineStr">
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
         <is>
           <t>\$#,0</t>
         </is>
       </c>
-      <c r="I35" s="25" t="inlineStr">
+      <c r="I39" s="25" t="inlineStr">
         <is>
           <t>$220,102</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="50" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>K-035</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
+    <row r="40" ht="50" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>K-039</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>03 Commercial</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>Revenue by Invoice Date</t>
         </is>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>Activates the inactive invoice-date relationship. Finance will want this view.</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>CALCULATE(
     [Net Revenue USD],
@@ -2771,178 +2963,178 @@
 )</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="F40" s="13" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
         <is>
           <t>\$#,0</t>
         </is>
       </c>
-      <c r="I36" s="18" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>K-036</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>K-040</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>03 Commercial</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>Revenue YTD</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr"/>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="D41" s="22" t="inlineStr"/>
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>TOTALYTD([Revenue by Invoice Date], dim_Date[Date])</t>
         </is>
       </c>
-      <c r="F37" s="20" t="inlineStr">
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G37" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H37" s="20" t="inlineStr">
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
         <is>
           <t>\$#,0</t>
         </is>
       </c>
-      <c r="I37" s="25" t="inlineStr">
+      <c r="I41" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>K-037</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>K-041</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>03 Commercial</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>Revenue PM</t>
         </is>
       </c>
-      <c r="D38" s="15" t="inlineStr"/>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr"/>
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>CALCULATE([Revenue by Invoice Date], PREVIOUSMONTH(dim_Date[Date]))</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="F42" s="13" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H38" s="13" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>\$#,0</t>
         </is>
       </c>
-      <c r="I38" s="18" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>K-038</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr">
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>K-042</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>03 Commercial</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>Revenue MoM %</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr"/>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="D43" s="22" t="inlineStr"/>
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>DIVIDE([Revenue by Invoice Date] - [Revenue PM], [Revenue PM])</t>
         </is>
       </c>
-      <c r="F39" s="20" t="inlineStr">
+      <c r="F43" s="20" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H39" s="20" t="inlineStr">
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I39" s="25" t="inlineStr">
+      <c r="I43" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="50" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>K-039</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
+    <row r="44" ht="50" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>K-043</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>03 Commercial</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>Revenue R3M Avg</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>Smooths the monthly noise.</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E44" s="16" t="inlineStr">
         <is>
           <t>CALCULATE(
     AVERAGEX(VALUES(dim_Date[Year_Month_Sort]), [Revenue by Invoice Date]),
@@ -2950,196 +3142,24 @@
 )</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H40" s="13" t="inlineStr">
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>\$#,0</t>
         </is>
       </c>
-      <c r="I40" s="18" t="inlineStr">
+      <c r="I44" s="18" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>K-040</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="inlineStr">
-        <is>
-          <t>03 Commercial</t>
-        </is>
-      </c>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>Realised Price PM</t>
-        </is>
-      </c>
-      <c r="D41" s="22" t="inlineStr"/>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>CALCULATE([Realised Price per MT], PREVIOUSMONTH(dim_Date[Date]))</t>
-        </is>
-      </c>
-      <c r="F41" s="20" t="inlineStr">
-        <is>
-          <t>fact_Invoice</t>
-        </is>
-      </c>
-      <c r="G41" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H41" s="20" t="inlineStr">
-        <is>
-          <t>\$#,0.00</t>
-        </is>
-      </c>
-      <c r="I41" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>K-041</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>03 Commercial</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>Realised Price MoM %</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr"/>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>DIVIDE([Realised Price per MT] - [Realised Price PM], [Realised Price PM])</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>fact_Invoice</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I42" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t>K-042</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>04 Price Bridge</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>Base Revenue</t>
-        </is>
-      </c>
-      <c r="D43" s="22" t="inlineStr"/>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>SUM(fact_Invoice[Base_Amount])</t>
-        </is>
-      </c>
-      <c r="F43" s="20" t="inlineStr">
-        <is>
-          <t>fact_Invoice</t>
-        </is>
-      </c>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H43" s="20" t="inlineStr">
-        <is>
-          <t>\$#,0</t>
-        </is>
-      </c>
-      <c r="I43" s="25" t="inlineStr">
-        <is>
-          <t>$8.95bn</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>K-043</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>04 Price Bridge</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="inlineStr">
-        <is>
-          <t>Regional Premium</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr"/>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>SUM(fact_Invoice[Regional_Premium])</t>
-        </is>
-      </c>
-      <c r="F44" s="13" t="inlineStr">
-        <is>
-          <t>fact_Invoice</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H44" s="13" t="inlineStr">
-        <is>
-          <t>\$#,0</t>
-        </is>
-      </c>
-      <c r="I44" s="18" t="inlineStr">
-        <is>
-          <t>$2.51bn</t>
         </is>
       </c>
     </row>
@@ -3151,18 +3171,18 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>04 Price Bridge</t>
+          <t>03 Commercial</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>Product Premium</t>
+          <t>Realised Price PM</t>
         </is>
       </c>
       <c r="D45" s="22" t="inlineStr"/>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>SUM(fact_Invoice[Product_Premium])</t>
+          <t>CALCULATE([Realised Price per MT], PREVIOUSMONTH(dim_Date[Date]))</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
@@ -3177,12 +3197,12 @@
       </c>
       <c r="H45" s="20" t="inlineStr">
         <is>
-          <t>\$#,0</t>
+          <t>\$#,0.00</t>
         </is>
       </c>
       <c r="I45" s="25" t="inlineStr">
         <is>
-          <t>$372.9m</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3194,18 +3214,18 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>04 Price Bridge</t>
+          <t>03 Commercial</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Green Premium</t>
+          <t>Realised Price MoM %</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr"/>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>SUM(fact_Invoice[Green_Premium])</t>
+          <t>DIVIDE([Realised Price per MT] - [Realised Price PM], [Realised Price PM])</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
@@ -3220,12 +3240,12 @@
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>\$#,0</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I46" s="18" t="inlineStr">
         <is>
-          <t>$7.5m</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3242,13 +3262,13 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>Other Premium</t>
+          <t>Base Revenue</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr"/>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>SUM(fact_Invoice[Other_Premium])</t>
+          <t>SUM(fact_Invoice[Base_Amount])</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
@@ -3268,7 +3288,7 @@
       </c>
       <c r="I47" s="25" t="inlineStr">
         <is>
-          <t>$0.2m</t>
+          <t>$8.95bn</t>
         </is>
       </c>
     </row>
@@ -3285,13 +3305,13 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Tariff Amount</t>
+          <t>Regional Premium</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr"/>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>SUM(fact_Invoice[Tariff_Amount])</t>
+          <t>SUM(fact_Invoice[Regional_Premium])</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
@@ -3311,7 +3331,7 @@
       </c>
       <c r="I48" s="18" t="inlineStr">
         <is>
-          <t>$28.4m</t>
+          <t>$2.51bn</t>
         </is>
       </c>
     </row>
@@ -3328,13 +3348,13 @@
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>Alloy Adjustment</t>
+          <t>Product Premium</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr"/>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>SUM(fact_Invoice[Alloy_Amount])</t>
+          <t>SUM(fact_Invoice[Product_Premium])</t>
         </is>
       </c>
       <c r="F49" s="20" t="inlineStr">
@@ -3354,7 +3374,7 @@
       </c>
       <c r="I49" s="25" t="inlineStr">
         <is>
-          <t>-$5.6m</t>
+          <t>$372.9m</t>
         </is>
       </c>
     </row>
@@ -3371,17 +3391,13 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Total Premium USD</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>All premium above the commodity base.</t>
-        </is>
-      </c>
+          <t>Green Premium</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr"/>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>[Regional Premium] + [Product Premium] + [Green Premium] + [Other Premium]</t>
+          <t>SUM(fact_Invoice[Green_Premium])</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
@@ -3401,7 +3417,7 @@
       </c>
       <c r="I50" s="18" t="inlineStr">
         <is>
-          <t>$2.89bn</t>
+          <t>$7.5m</t>
         </is>
       </c>
     </row>
@@ -3418,17 +3434,13 @@
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>Bridge MT</t>
-        </is>
-      </c>
-      <c r="D51" s="22" t="inlineStr">
-        <is>
-          <t>Volume on lines carrying a full price breakdown.</t>
-        </is>
-      </c>
+          <t>Other Premium</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr"/>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>CALCULATE([Invoiced MT], fact_Invoice[Has_Price_Bridge] = TRUE())</t>
+          <t>SUM(fact_Invoice[Other_Premium])</t>
         </is>
       </c>
       <c r="F51" s="20" t="inlineStr">
@@ -3443,12 +3455,12 @@
       </c>
       <c r="H51" s="20" t="inlineStr">
         <is>
-          <t>#,0</t>
+          <t>\$#,0</t>
         </is>
       </c>
       <c r="I51" s="25" t="inlineStr">
         <is>
-          <t>11,124,100</t>
+          <t>$0.2m</t>
         </is>
       </c>
     </row>
@@ -3465,13 +3477,13 @@
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Bridge Revenue USD</t>
+          <t>Tariff Amount</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr"/>
       <c r="E52" s="16" t="inlineStr">
         <is>
-          <t>CALCULATE([Net Revenue USD], fact_Invoice[Has_Price_Bridge] = TRUE())</t>
+          <t>SUM(fact_Invoice[Tariff_Amount])</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
@@ -3491,7 +3503,7 @@
       </c>
       <c r="I52" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$28.4m</t>
         </is>
       </c>
     </row>
@@ -3508,17 +3520,13 @@
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>Price Bridge Coverage %</t>
-        </is>
-      </c>
-      <c r="D53" s="22" t="inlineStr">
-        <is>
-          <t>How much of revenue the bridge explains. SAM and AUS carry none — always show this next to a bridge visual.</t>
-        </is>
-      </c>
+          <t>Alloy Adjustment</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="inlineStr"/>
       <c r="E53" s="23" t="inlineStr">
         <is>
-          <t>DIVIDE([Bridge Revenue USD], [Net Revenue USD])</t>
+          <t>SUM(fact_Invoice[Alloy_Amount])</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
@@ -3533,12 +3541,12 @@
       </c>
       <c r="H53" s="20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>\$#,0</t>
         </is>
       </c>
       <c r="I53" s="25" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>-$5.6m</t>
         </is>
       </c>
     </row>
@@ -3555,17 +3563,17 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Premium % of Revenue</t>
+          <t>Total Premium USD</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>Denominator restricted to bridge-covered lines, so the ratio is honest.</t>
+          <t>All premium above the commodity base.</t>
         </is>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
-          <t>DIVIDE([Total Premium USD], [Bridge Revenue USD])</t>
+          <t>[Regional Premium] + [Product Premium] + [Green Premium] + [Other Premium]</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
@@ -3580,12 +3588,12 @@
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>\$#,0</t>
         </is>
       </c>
       <c r="I54" s="18" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>$2.89bn</t>
         </is>
       </c>
     </row>
@@ -3602,13 +3610,17 @@
       </c>
       <c r="C55" s="21" t="inlineStr">
         <is>
-          <t>Base Price per MT</t>
-        </is>
-      </c>
-      <c r="D55" s="22" t="inlineStr"/>
+          <t>Bridge MT</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>Volume on lines carrying a full price breakdown.</t>
+        </is>
+      </c>
       <c r="E55" s="23" t="inlineStr">
         <is>
-          <t>DIVIDE([Base Revenue], [Bridge MT])</t>
+          <t>CALCULATE([Invoiced MT], fact_Invoice[Has_Price_Bridge] = TRUE())</t>
         </is>
       </c>
       <c r="F55" s="20" t="inlineStr">
@@ -3623,12 +3635,12 @@
       </c>
       <c r="H55" s="20" t="inlineStr">
         <is>
-          <t>\$#,0.00</t>
+          <t>#,0</t>
         </is>
       </c>
       <c r="I55" s="25" t="inlineStr">
         <is>
-          <t>$804.60</t>
+          <t>11,124,100</t>
         </is>
       </c>
     </row>
@@ -3645,13 +3657,13 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Regional Premium per MT</t>
+          <t>Bridge Revenue USD</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr"/>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>DIVIDE([Regional Premium], [Bridge MT])</t>
+          <t>CALCULATE([Net Revenue USD], fact_Invoice[Has_Price_Bridge] = TRUE())</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -3666,7 +3678,7 @@
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>\$#,0.00</t>
+          <t>\$#,0</t>
         </is>
       </c>
       <c r="I56" s="18" t="inlineStr">
@@ -3688,13 +3700,17 @@
       </c>
       <c r="C57" s="21" t="inlineStr">
         <is>
-          <t>Product Premium per MT</t>
-        </is>
-      </c>
-      <c r="D57" s="22" t="inlineStr"/>
+          <t>Price Bridge Coverage %</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="inlineStr">
+        <is>
+          <t>How much of revenue the bridge explains. SAM and AUS carry none — always show this next to a bridge visual.</t>
+        </is>
+      </c>
       <c r="E57" s="23" t="inlineStr">
         <is>
-          <t>DIVIDE([Product Premium], [Bridge MT])</t>
+          <t>DIVIDE([Bridge Revenue USD], [Net Revenue USD])</t>
         </is>
       </c>
       <c r="F57" s="20" t="inlineStr">
@@ -3709,12 +3725,12 @@
       </c>
       <c r="H57" s="20" t="inlineStr">
         <is>
-          <t>\$#,0.00</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I57" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -3731,13 +3747,17 @@
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Green Premium per MT</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="inlineStr"/>
+          <t>Premium % of Revenue</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>Denominator restricted to bridge-covered lines, so the ratio is honest.</t>
+        </is>
+      </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>DIVIDE([Green Premium], [Bridge MT])</t>
+          <t>DIVIDE([Total Premium USD], [Bridge Revenue USD])</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
@@ -3752,12 +3772,12 @@
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t>\$#,0.00</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I58" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
@@ -3774,13 +3794,13 @@
       </c>
       <c r="C59" s="21" t="inlineStr">
         <is>
-          <t>Premium per MT</t>
+          <t>Base Price per MT</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr"/>
       <c r="E59" s="23" t="inlineStr">
         <is>
-          <t>DIVIDE([Total Premium USD], [Bridge MT])</t>
+          <t>DIVIDE([Base Revenue], [Bridge MT])</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
@@ -3800,7 +3820,7 @@
       </c>
       <c r="I59" s="25" t="inlineStr">
         <is>
-          <t>$259.57</t>
+          <t>$804.60</t>
         </is>
       </c>
     </row>
@@ -3817,62 +3837,234 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
+          <t>Regional Premium per MT</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr"/>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>DIVIDE([Regional Premium], [Bridge MT])</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>fact_Invoice</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>\$#,0.00</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>K-060</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>04 Price Bridge</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="inlineStr">
+        <is>
+          <t>Product Premium per MT</t>
+        </is>
+      </c>
+      <c r="D61" s="22" t="inlineStr"/>
+      <c r="E61" s="23" t="inlineStr">
+        <is>
+          <t>DIVIDE([Product Premium], [Bridge MT])</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>fact_Invoice</t>
+        </is>
+      </c>
+      <c r="G61" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H61" s="20" t="inlineStr">
+        <is>
+          <t>\$#,0.00</t>
+        </is>
+      </c>
+      <c r="I61" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>K-061</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>04 Price Bridge</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Green Premium per MT</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr"/>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>DIVIDE([Green Premium], [Bridge MT])</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>fact_Invoice</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>\$#,0.00</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>K-062</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>04 Price Bridge</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="inlineStr">
+        <is>
+          <t>Premium per MT</t>
+        </is>
+      </c>
+      <c r="D63" s="22" t="inlineStr"/>
+      <c r="E63" s="23" t="inlineStr">
+        <is>
+          <t>DIVIDE([Total Premium USD], [Bridge MT])</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>fact_Invoice</t>
+        </is>
+      </c>
+      <c r="G63" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>\$#,0.00</t>
+        </is>
+      </c>
+      <c r="I63" s="25" t="inlineStr">
+        <is>
+          <t>$259.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>K-063</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>04 Price Bridge</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
           <t>Bridge Realised Price per MT</t>
         </is>
       </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>Components reconcile to this within 0.7%.</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="E64" s="16" t="inlineStr">
         <is>
           <t>DIVIDE([Bridge Revenue USD], [Bridge MT])</t>
         </is>
       </c>
-      <c r="F60" s="13" t="inlineStr">
+      <c r="F64" s="13" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H60" s="13" t="inlineStr">
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
         <is>
           <t>\$#,0.00</t>
         </is>
       </c>
-      <c r="I60" s="18" t="inlineStr">
+      <c r="I64" s="18" t="inlineStr">
         <is>
           <t>$1,058.68</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="50" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
-        <is>
-          <t>K-060</t>
-        </is>
-      </c>
-      <c r="B61" s="20" t="inlineStr">
+    <row r="65" ht="50" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>K-064</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
         <is>
           <t>04 Price Bridge</t>
         </is>
       </c>
-      <c r="C61" s="21" t="inlineStr">
+      <c r="C65" s="21" t="inlineStr">
         <is>
           <t>Green Premium Penetration %</t>
         </is>
       </c>
-      <c r="D61" s="22" t="inlineStr">
+      <c r="D65" s="22" t="inlineStr">
         <is>
           <t>Share of invoice lines carrying a green premium.</t>
         </is>
       </c>
-      <c r="E61" s="23" t="inlineStr">
+      <c r="E65" s="23" t="inlineStr">
         <is>
           <t>DIVIDE(
     CALCULATE(COUNTROWS(fact_Invoice), fact_Invoice[Green_Premium] &lt;&gt; 0),
@@ -3880,221 +4072,221 @@
 )</t>
         </is>
       </c>
-      <c r="F61" s="20" t="inlineStr">
+      <c r="F65" s="20" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G61" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H61" s="20" t="inlineStr">
+      <c r="G65" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H65" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I61" s="25" t="inlineStr">
+      <c r="I65" s="25" t="inlineStr">
         <is>
           <t>9.3%</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="26" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>K-061</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>K-065</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>05 Revenue Quality</t>
         </is>
       </c>
-      <c r="C62" s="14" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>Credit Rate %</t>
         </is>
       </c>
-      <c r="D62" s="15" t="inlineStr">
+      <c r="D66" s="15" t="inlineStr">
         <is>
           <t>Billing accuracy in one number.</t>
         </is>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="E66" s="16" t="inlineStr">
         <is>
           <t>DIVIDE(ABS([Credits USD]), [Gross Revenue USD])</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G62" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H62" s="13" t="inlineStr">
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H66" s="13" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="I62" s="18" t="inlineStr">
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="19" t="inlineStr">
-        <is>
-          <t>K-062</t>
-        </is>
-      </c>
-      <c r="B63" s="20" t="inlineStr">
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>K-066</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
         <is>
           <t>05 Revenue Quality</t>
         </is>
       </c>
-      <c r="C63" s="21" t="inlineStr">
+      <c r="C67" s="21" t="inlineStr">
         <is>
           <t>Credit Memo Lines</t>
         </is>
       </c>
-      <c r="D63" s="22" t="inlineStr"/>
-      <c r="E63" s="23" t="inlineStr">
+      <c r="D67" s="22" t="inlineStr"/>
+      <c r="E67" s="23" t="inlineStr">
         <is>
           <t>CALCULATE(COUNTROWS(fact_Invoice), fact_Invoice[Is_Credit_Memo] = TRUE())</t>
         </is>
       </c>
-      <c r="F63" s="20" t="inlineStr">
+      <c r="F67" s="20" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G63" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H63" s="20" t="inlineStr">
+      <c r="G67" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H67" s="20" t="inlineStr">
         <is>
           <t>#,0</t>
         </is>
       </c>
-      <c r="I63" s="25" t="inlineStr">
+      <c r="I67" s="25" t="inlineStr">
         <is>
           <t>4,924</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="26" customHeight="1">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t>K-063</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>K-067</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>05 Revenue Quality</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>Credit Memo Rate %</t>
         </is>
       </c>
-      <c r="D64" s="15" t="inlineStr"/>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="D68" s="15" t="inlineStr"/>
+      <c r="E68" s="16" t="inlineStr">
         <is>
           <t>DIVIDE([Credit Memo Lines], COUNTROWS(fact_Invoice))</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr">
+      <c r="F68" s="13" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G64" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H64" s="13" t="inlineStr">
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I64" s="18" t="inlineStr">
+      <c r="I68" s="18" t="inlineStr">
         <is>
           <t>6.19%</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="26" customHeight="1">
-      <c r="A65" s="19" t="inlineStr">
-        <is>
-          <t>K-064</t>
-        </is>
-      </c>
-      <c r="B65" s="20" t="inlineStr">
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>K-068</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="inlineStr">
         <is>
           <t>05 Revenue Quality</t>
         </is>
       </c>
-      <c r="C65" s="21" t="inlineStr">
+      <c r="C69" s="21" t="inlineStr">
         <is>
           <t>Avg Credit Value</t>
         </is>
       </c>
-      <c r="D65" s="22" t="inlineStr"/>
-      <c r="E65" s="23" t="inlineStr">
+      <c r="D69" s="22" t="inlineStr"/>
+      <c r="E69" s="23" t="inlineStr">
         <is>
           <t>DIVIDE([Credits USD], [Credit Memo Lines])</t>
         </is>
       </c>
-      <c r="F65" s="20" t="inlineStr">
+      <c r="F69" s="20" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G65" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H65" s="20" t="inlineStr">
+      <c r="G69" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H69" s="20" t="inlineStr">
         <is>
           <t>\$#,0</t>
         </is>
       </c>
-      <c r="I65" s="25" t="inlineStr">
+      <c r="I69" s="25" t="inlineStr">
         <is>
           <t>-$46,652</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="50" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>K-065</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
+    <row r="70" ht="50" customHeight="1">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>K-069</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>05 Revenue Quality</t>
         </is>
       </c>
-      <c r="C66" s="14" t="inlineStr">
+      <c r="C70" s="14" t="inlineStr">
         <is>
           <t>Credits by Invoice Date</t>
         </is>
       </c>
-      <c r="D66" s="15" t="inlineStr"/>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="D70" s="15" t="inlineStr"/>
+      <c r="E70" s="16" t="inlineStr">
         <is>
           <t>CALCULATE(
     [Credits USD],
@@ -4102,49 +4294,49 @@
 )</t>
         </is>
       </c>
-      <c r="F66" s="13" t="inlineStr">
+      <c r="F70" s="13" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G66" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H66" s="13" t="inlineStr">
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H70" s="13" t="inlineStr">
         <is>
           <t>\$#,0</t>
         </is>
       </c>
-      <c r="I66" s="18" t="inlineStr">
+      <c r="I70" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="71" customHeight="1">
-      <c r="A67" s="19" t="inlineStr">
-        <is>
-          <t>K-066</t>
-        </is>
-      </c>
-      <c r="B67" s="20" t="inlineStr">
+    <row r="71" ht="71" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>K-070</t>
+        </is>
+      </c>
+      <c r="B71" s="20" t="inlineStr">
         <is>
           <t>05 Revenue Quality</t>
         </is>
       </c>
-      <c r="C67" s="21" t="inlineStr">
+      <c r="C71" s="21" t="inlineStr">
         <is>
           <t>Credit Rate by Invoice Date</t>
         </is>
       </c>
-      <c r="D67" s="22" t="inlineStr">
+      <c r="D71" s="22" t="inlineStr">
         <is>
           <t>The trend that matters. On the order-date timeline the spike is invisible.</t>
         </is>
       </c>
-      <c r="E67" s="23" t="inlineStr">
+      <c r="E71" s="23" t="inlineStr">
         <is>
           <t>VAR G =
     CALCULATE([Gross Revenue USD], USERELATIONSHIP(dim_Date[Date], fact_Invoice[Invoice_Date]))
@@ -4154,49 +4346,49 @@
     DIVIDE(ABS(C), G)</t>
         </is>
       </c>
-      <c r="F67" s="20" t="inlineStr">
+      <c r="F71" s="20" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G67" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H67" s="20" t="inlineStr">
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H71" s="20" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="I67" s="25" t="inlineStr">
+      <c r="I71" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="102.5" customHeight="1">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>K-067</t>
-        </is>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
+    <row r="72" ht="102.5" customHeight="1">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>K-071</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>05 Revenue Quality</t>
         </is>
       </c>
-      <c r="C68" s="14" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>Credit Rate Status</t>
         </is>
       </c>
-      <c r="D68" s="15" t="inlineStr">
+      <c r="D72" s="15" t="inlineStr">
         <is>
           <t>Traffic light against a 1% watch and 2% critical threshold.</t>
         </is>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E72" s="16" t="inlineStr">
         <is>
           <t>VAR r = [Credit Rate by Invoice Date]
 RETURN
@@ -4209,199 +4401,19 @@
     )</t>
         </is>
       </c>
-      <c r="F68" s="13" t="inlineStr">
+      <c r="F72" s="13" t="inlineStr">
         <is>
           <t>fact_Invoice</t>
         </is>
       </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H68" s="13" t="inlineStr">
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
         <is>
           <t>text</t>
-        </is>
-      </c>
-      <c r="I68" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="26" customHeight="1">
-      <c r="A69" s="19" t="inlineStr">
-        <is>
-          <t>K-068</t>
-        </is>
-      </c>
-      <c r="B69" s="20" t="inlineStr">
-        <is>
-          <t>06 Order to Cash</t>
-        </is>
-      </c>
-      <c r="C69" s="21" t="inlineStr">
-        <is>
-          <t>Fulfilment Rate %</t>
-        </is>
-      </c>
-      <c r="D69" s="22" t="inlineStr">
-        <is>
-          <t>Share of ordered volume shipped.</t>
-        </is>
-      </c>
-      <c r="E69" s="23" t="inlineStr">
-        <is>
-          <t>DIVIDE([Shipped MT Order View], [Ordered MT])</t>
-        </is>
-      </c>
-      <c r="F69" s="20" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="G69" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H69" s="20" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I69" s="25" t="inlineStr">
-        <is>
-          <t>80.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="26" customHeight="1">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>K-069</t>
-        </is>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>06 Order to Cash</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>Billing Rate %</t>
-        </is>
-      </c>
-      <c r="D70" s="15" t="inlineStr">
-        <is>
-          <t>Share of shipped volume invoiced.</t>
-        </is>
-      </c>
-      <c r="E70" s="16" t="inlineStr">
-        <is>
-          <t>DIVIDE([Invoiced MT], [Shipped MT Order View])</t>
-        </is>
-      </c>
-      <c r="F70" s="13" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="G70" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H70" s="13" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I70" s="18" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="26" customHeight="1">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>K-070</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="inlineStr">
-        <is>
-          <t>06 Order to Cash</t>
-        </is>
-      </c>
-      <c r="C71" s="21" t="inlineStr">
-        <is>
-          <t>OTC Conversion %</t>
-        </is>
-      </c>
-      <c r="D71" s="22" t="inlineStr"/>
-      <c r="E71" s="23" t="inlineStr">
-        <is>
-          <t>DIVIDE([Invoiced MT], [Ordered MT])</t>
-        </is>
-      </c>
-      <c r="F71" s="20" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="G71" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H71" s="20" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I71" s="25" t="inlineStr">
-        <is>
-          <t>80.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="26" customHeight="1">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t>K-071</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
-        <is>
-          <t>06 Order to Cash</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>Open to Ship MT</t>
-        </is>
-      </c>
-      <c r="D72" s="15" t="inlineStr"/>
-      <c r="E72" s="16" t="inlineStr">
-        <is>
-          <t>[Ordered MT] - [Shipped MT Order View]</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="G72" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H72" s="13" t="inlineStr">
-        <is>
-          <t>#,0</t>
         </is>
       </c>
       <c r="I72" s="18" t="inlineStr">
@@ -4423,17 +4435,17 @@
       </c>
       <c r="C73" s="21" t="inlineStr">
         <is>
-          <t>Unbilled Shipped MT</t>
+          <t>Fulfilment Rate %</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Shipped but not invoiced. Should sit near zero.</t>
+          <t>Share of ordered volume shipped.</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>[Shipped MT Order View] - [Invoiced MT]</t>
+          <t>DIVIDE([Shipped MT Order View], [Ordered MT])</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
@@ -4448,12 +4460,12 @@
       </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
-          <t>#,0</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I73" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80.3%</t>
         </is>
       </c>
     </row>
@@ -4470,13 +4482,17 @@
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Backlog MT</t>
-        </is>
-      </c>
-      <c r="D74" s="15" t="inlineStr"/>
+          <t>Billing Rate %</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Share of shipped volume invoiced.</t>
+        </is>
+      </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
-          <t>CALCULATE([Ordered MT], dim_SalesOrderLine[Is_Open] = TRUE())</t>
+          <t>DIVIDE([Invoiced MT], [Shipped MT Order View])</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
@@ -4491,12 +4507,12 @@
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>#,0</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I74" s="18" t="inlineStr">
         <is>
-          <t>4,225,606</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4513,13 +4529,13 @@
       </c>
       <c r="C75" s="21" t="inlineStr">
         <is>
-          <t>Open Order Lines</t>
+          <t>OTC Conversion %</t>
         </is>
       </c>
       <c r="D75" s="22" t="inlineStr"/>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>CALCULATE([Order Lines], dim_SalesOrderLine[Is_Open] = TRUE())</t>
+          <t>DIVIDE([Invoiced MT], [Ordered MT])</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
@@ -4534,12 +4550,12 @@
       </c>
       <c r="H75" s="20" t="inlineStr">
         <is>
-          <t>#,0</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I75" s="25" t="inlineStr">
         <is>
-          <t>5,369</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -4556,17 +4572,13 @@
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Cancelled Lines</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>Should be zero — the source query intends to exclude these. See the SQL precedence note.</t>
-        </is>
-      </c>
+          <t>Open to Ship MT</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr"/>
       <c r="E76" s="16" t="inlineStr">
         <is>
-          <t>CALCULATE([Order Lines], dim_SalesOrderLine[Is_Cancelled] = TRUE())</t>
+          <t>[Ordered MT] - [Shipped MT Order View]</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
@@ -4586,7 +4598,7 @@
       </c>
       <c r="I76" s="18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4603,58 +4615,238 @@
       </c>
       <c r="C77" s="21" t="inlineStr">
         <is>
+          <t>Unbilled Shipped MT</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="inlineStr">
+        <is>
+          <t>Shipped but not invoiced. Should sit near zero.</t>
+        </is>
+      </c>
+      <c r="E77" s="23" t="inlineStr">
+        <is>
+          <t>[Shipped MT Order View] - [Invoiced MT]</t>
+        </is>
+      </c>
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H77" s="20" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I77" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>K-077</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>06 Order to Cash</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>Backlog MT</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr"/>
+      <c r="E78" s="16" t="inlineStr">
+        <is>
+          <t>CALCULATE([Ordered MT], dim_SalesOrderLine[Is_Open] = TRUE())</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I78" s="18" t="inlineStr">
+        <is>
+          <t>4,225,606</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="26" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>K-078</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>06 Order to Cash</t>
+        </is>
+      </c>
+      <c r="C79" s="21" t="inlineStr">
+        <is>
+          <t>Open Order Lines</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="inlineStr"/>
+      <c r="E79" s="23" t="inlineStr">
+        <is>
+          <t>CALCULATE([Order Lines], dim_SalesOrderLine[Is_Open] = TRUE())</t>
+        </is>
+      </c>
+      <c r="F79" s="20" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H79" s="20" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I79" s="25" t="inlineStr">
+        <is>
+          <t>5,369</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="26" customHeight="1">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>K-079</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>06 Order to Cash</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>Cancelled Lines</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>Should be zero — the source query intends to exclude these. See the SQL precedence note.</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
+          <t>CALCULATE([Order Lines], dim_SalesOrderLine[Is_Cancelled] = TRUE())</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>K-080</t>
+        </is>
+      </c>
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>06 Order to Cash</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="inlineStr">
+        <is>
           <t>Cancellation Rate %</t>
         </is>
       </c>
-      <c r="D77" s="22" t="inlineStr"/>
-      <c r="E77" s="23" t="inlineStr">
+      <c r="D81" s="22" t="inlineStr"/>
+      <c r="E81" s="23" t="inlineStr">
         <is>
           <t>DIVIDE([Cancelled Lines], [Order Lines])</t>
         </is>
       </c>
-      <c r="F77" s="20" t="inlineStr">
+      <c r="F81" s="20" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G77" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H77" s="20" t="inlineStr">
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H81" s="20" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="I77" s="25" t="inlineStr">
-        <is>
-          <t>0.06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="81.5" customHeight="1">
-      <c r="A78" s="12" t="inlineStr">
-        <is>
-          <t>K-077</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
+      <c r="I81" s="25" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="81.5" customHeight="1">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>K-081</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>06 Order to Cash</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
+      <c r="C82" s="14" t="inlineStr">
         <is>
           <t>Backlog Coverage Days</t>
         </is>
       </c>
-      <c r="D78" s="15" t="inlineStr">
+      <c r="D82" s="15" t="inlineStr">
         <is>
           <t>How many days of recent shipping the order book represents.</t>
         </is>
       </c>
-      <c r="E78" s="16" t="inlineStr">
+      <c r="E82" s="16" t="inlineStr">
         <is>
           <t>VAR RecentShipped =
     CALCULATE(
@@ -4665,92 +4857,92 @@
     DIVIDE([Backlog MT], DIVIDE(RecentShipped, 90))</t>
         </is>
       </c>
-      <c r="F78" s="13" t="inlineStr">
+      <c r="F82" s="13" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G78" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H78" s="13" t="inlineStr">
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H82" s="13" t="inlineStr">
         <is>
           <t>#,0.0</t>
         </is>
       </c>
-      <c r="I78" s="18" t="inlineStr">
+      <c r="I82" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="26" customHeight="1">
-      <c r="A79" s="19" t="inlineStr">
-        <is>
-          <t>K-078</t>
-        </is>
-      </c>
-      <c r="B79" s="20" t="inlineStr">
+    <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>K-082</t>
+        </is>
+      </c>
+      <c r="B83" s="20" t="inlineStr">
         <is>
           <t>07 Service</t>
         </is>
       </c>
-      <c r="C79" s="21" t="inlineStr">
+      <c r="C83" s="21" t="inlineStr">
         <is>
           <t>Lines Shipped</t>
         </is>
       </c>
-      <c r="D79" s="22" t="inlineStr"/>
-      <c r="E79" s="23" t="inlineStr">
+      <c r="D83" s="22" t="inlineStr"/>
+      <c r="E83" s="23" t="inlineStr">
         <is>
           <t>CALCULATE([Order Lines], NOT ISBLANK(dim_SalesOrderLine[Actual_Shipment_Date]))</t>
         </is>
       </c>
-      <c r="F79" s="20" t="inlineStr">
+      <c r="F83" s="20" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G79" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H79" s="20" t="inlineStr">
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H83" s="20" t="inlineStr">
         <is>
           <t>#,0</t>
         </is>
       </c>
-      <c r="I79" s="25" t="inlineStr">
+      <c r="I83" s="25" t="inlineStr">
         <is>
           <t>58,906</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="113" customHeight="1">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t>K-079</t>
-        </is>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
+    <row r="84" ht="113" customHeight="1">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>K-083</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>07 Service</t>
         </is>
       </c>
-      <c r="C80" s="14" t="inlineStr">
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>On Time vs Schedule %</t>
         </is>
       </c>
-      <c r="D80" s="15" t="inlineStr">
+      <c r="D84" s="15" t="inlineStr">
         <is>
           <t>The internal-commitment view.</t>
         </is>
       </c>
-      <c r="E80" s="16" t="inlineStr">
+      <c r="E84" s="16" t="inlineStr">
         <is>
           <t>VAR Base =
     CALCULATE(
@@ -4764,49 +4956,49 @@
     DIVIDE(OnTime, Base)</t>
         </is>
       </c>
-      <c r="F80" s="13" t="inlineStr">
+      <c r="F84" s="13" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G80" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H80" s="13" t="inlineStr">
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H84" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I80" s="18" t="inlineStr">
-        <is>
-          <t>56.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="160" customHeight="1">
-      <c r="A81" s="19" t="inlineStr">
-        <is>
-          <t>K-080</t>
-        </is>
-      </c>
-      <c r="B81" s="20" t="inlineStr">
+      <c r="I84" s="18" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="160" customHeight="1">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>K-084</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="inlineStr">
         <is>
           <t>07 Service</t>
         </is>
       </c>
-      <c r="C81" s="21" t="inlineStr">
+      <c r="C85" s="21" t="inlineStr">
         <is>
           <t>On Time vs Promise %</t>
         </is>
       </c>
-      <c r="D81" s="22" t="inlineStr">
+      <c r="D85" s="22" t="inlineStr">
         <is>
           <t>The customer-facing view, and the weakest of the three.</t>
         </is>
       </c>
-      <c r="E81" s="23" t="inlineStr">
+      <c r="E85" s="23" t="inlineStr">
         <is>
           <t>VAR Base =
     CALCULATE(
@@ -4826,45 +5018,45 @@
     DIVIDE(OnTime, Base)</t>
         </is>
       </c>
-      <c r="F81" s="20" t="inlineStr">
+      <c r="F85" s="20" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G81" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H81" s="20" t="inlineStr">
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H85" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I81" s="25" t="inlineStr">
-        <is>
-          <t>40.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="160" customHeight="1">
-      <c r="A82" s="12" t="inlineStr">
-        <is>
-          <t>K-081</t>
-        </is>
-      </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="I85" s="25" t="inlineStr">
+        <is>
+          <t>54.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="160" customHeight="1">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>K-085</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>07 Service</t>
         </is>
       </c>
-      <c r="C82" s="14" t="inlineStr">
+      <c r="C86" s="14" t="inlineStr">
         <is>
           <t>On Time vs Request %</t>
         </is>
       </c>
-      <c r="D82" s="15" t="inlineStr"/>
-      <c r="E82" s="16" t="inlineStr">
+      <c r="D86" s="15" t="inlineStr"/>
+      <c r="E86" s="16" t="inlineStr">
         <is>
           <t>VAR Base =
     CALCULATE(
@@ -4884,204 +5076,24 @@
     DIVIDE(OnTime, Base)</t>
         </is>
       </c>
-      <c r="F82" s="13" t="inlineStr">
+      <c r="F86" s="13" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G82" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H82" s="13" t="inlineStr">
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H86" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I82" s="18" t="inlineStr">
+      <c r="I86" s="18" t="inlineStr">
         <is>
           <t>44.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="26" customHeight="1">
-      <c r="A83" s="19" t="inlineStr">
-        <is>
-          <t>K-082</t>
-        </is>
-      </c>
-      <c r="B83" s="20" t="inlineStr">
-        <is>
-          <t>07 Service</t>
-        </is>
-      </c>
-      <c r="C83" s="21" t="inlineStr">
-        <is>
-          <t>Lines Shipped Late</t>
-        </is>
-      </c>
-      <c r="D83" s="22" t="inlineStr"/>
-      <c r="E83" s="23" t="inlineStr">
-        <is>
-          <t>CALCULATE([Order Lines], dim_SalesOrderLine[Ship_Delay_Days] &gt; 0)</t>
-        </is>
-      </c>
-      <c r="F83" s="20" t="inlineStr">
-        <is>
-          <t>dim_SalesOrderLine</t>
-        </is>
-      </c>
-      <c r="G83" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H83" s="20" t="inlineStr">
-        <is>
-          <t>#,0</t>
-        </is>
-      </c>
-      <c r="I83" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="26" customHeight="1">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t>K-083</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="inlineStr">
-        <is>
-          <t>07 Service</t>
-        </is>
-      </c>
-      <c r="C84" s="14" t="inlineStr">
-        <is>
-          <t>Lines 30d+ Late</t>
-        </is>
-      </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>The tail that costs relationships.</t>
-        </is>
-      </c>
-      <c r="E84" s="16" t="inlineStr">
-        <is>
-          <t>CALCULATE([Order Lines], dim_SalesOrderLine[Ship_Delay_Days] &gt; 30)</t>
-        </is>
-      </c>
-      <c r="F84" s="13" t="inlineStr">
-        <is>
-          <t>dim_SalesOrderLine</t>
-        </is>
-      </c>
-      <c r="G84" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H84" s="13" t="inlineStr">
-        <is>
-          <t>#,0</t>
-        </is>
-      </c>
-      <c r="I84" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="26" customHeight="1">
-      <c r="A85" s="19" t="inlineStr">
-        <is>
-          <t>K-084</t>
-        </is>
-      </c>
-      <c r="B85" s="20" t="inlineStr">
-        <is>
-          <t>07 Service</t>
-        </is>
-      </c>
-      <c r="C85" s="21" t="inlineStr">
-        <is>
-          <t>Avg Ship Delay Days</t>
-        </is>
-      </c>
-      <c r="D85" s="22" t="inlineStr">
-        <is>
-          <t>Skewed by the tail — read alongside the median.</t>
-        </is>
-      </c>
-      <c r="E85" s="23" t="inlineStr">
-        <is>
-          <t>AVERAGE(dim_SalesOrderLine[Ship_Delay_Days])</t>
-        </is>
-      </c>
-      <c r="F85" s="20" t="inlineStr">
-        <is>
-          <t>dim_SalesOrderLine</t>
-        </is>
-      </c>
-      <c r="G85" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H85" s="20" t="inlineStr">
-        <is>
-          <t>#,0.0</t>
-        </is>
-      </c>
-      <c r="I85" s="25" t="inlineStr">
-        <is>
-          <t>14.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="26" customHeight="1">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
-          <t>K-085</t>
-        </is>
-      </c>
-      <c r="B86" s="13" t="inlineStr">
-        <is>
-          <t>07 Service</t>
-        </is>
-      </c>
-      <c r="C86" s="14" t="inlineStr">
-        <is>
-          <t>Median Ship Delay Days</t>
-        </is>
-      </c>
-      <c r="D86" s="15" t="inlineStr"/>
-      <c r="E86" s="16" t="inlineStr">
-        <is>
-          <t>MEDIAN(dim_SalesOrderLine[Ship_Delay_Days])</t>
-        </is>
-      </c>
-      <c r="F86" s="13" t="inlineStr">
-        <is>
-          <t>dim_SalesOrderLine</t>
-        </is>
-      </c>
-      <c r="G86" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H86" s="13" t="inlineStr">
-        <is>
-          <t>#,0.0</t>
-        </is>
-      </c>
-      <c r="I86" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -5098,17 +5110,13 @@
       </c>
       <c r="C87" s="21" t="inlineStr">
         <is>
-          <t>Median Cycle Days</t>
-        </is>
-      </c>
-      <c r="D87" s="22" t="inlineStr">
-        <is>
-          <t>Report this, not the mean. The mean is roughly double.</t>
-        </is>
-      </c>
+          <t>Lines Shipped Late</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="inlineStr"/>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>MEDIAN(dim_SalesOrderLine[Days_Order_To_Ship])</t>
+          <t>CALCULATE([Order Lines], dim_SalesOrderLine[Ship_Delay_Days] &gt; 0)</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
@@ -5123,12 +5131,12 @@
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>#,0.0</t>
+          <t>#,0</t>
         </is>
       </c>
       <c r="I87" s="25" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5145,13 +5153,17 @@
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Avg Cycle Days</t>
-        </is>
-      </c>
-      <c r="D88" s="15" t="inlineStr"/>
+          <t>Lines 30d+ Late</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>The tail that costs relationships.</t>
+        </is>
+      </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
-          <t>AVERAGE(dim_SalesOrderLine[Days_Order_To_Ship])</t>
+          <t>CALCULATE([Order Lines], dim_SalesOrderLine[Ship_Delay_Days] &gt; 30)</t>
         </is>
       </c>
       <c r="F88" s="13" t="inlineStr">
@@ -5166,12 +5178,12 @@
       </c>
       <c r="H88" s="13" t="inlineStr">
         <is>
-          <t>#,0.0</t>
+          <t>#,0</t>
         </is>
       </c>
       <c r="I88" s="18" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5188,62 +5200,242 @@
       </c>
       <c r="C89" s="21" t="inlineStr">
         <is>
+          <t>Avg Ship Delay Days</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="inlineStr">
+        <is>
+          <t>Skewed by the tail — read alongside the median.</t>
+        </is>
+      </c>
+      <c r="E89" s="23" t="inlineStr">
+        <is>
+          <t>AVERAGE(dim_SalesOrderLine[Ship_Delay_Days])</t>
+        </is>
+      </c>
+      <c r="F89" s="20" t="inlineStr">
+        <is>
+          <t>dim_SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H89" s="20" t="inlineStr">
+        <is>
+          <t>#,0.0</t>
+        </is>
+      </c>
+      <c r="I89" s="25" t="inlineStr">
+        <is>
+          <t>14.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>K-089</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>07 Service</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>Median Ship Delay Days</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr"/>
+      <c r="E90" s="16" t="inlineStr">
+        <is>
+          <t>MEDIAN(dim_SalesOrderLine[Ship_Delay_Days])</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="inlineStr">
+        <is>
+          <t>dim_SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H90" s="13" t="inlineStr">
+        <is>
+          <t>#,0.0</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="26" customHeight="1">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>K-090</t>
+        </is>
+      </c>
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>07 Service</t>
+        </is>
+      </c>
+      <c r="C91" s="21" t="inlineStr">
+        <is>
+          <t>Median Cycle Days</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="inlineStr">
+        <is>
+          <t>Report this, not the mean. The mean is roughly double.</t>
+        </is>
+      </c>
+      <c r="E91" s="23" t="inlineStr">
+        <is>
+          <t>MEDIAN(dim_SalesOrderLine[Days_Order_To_Ship])</t>
+        </is>
+      </c>
+      <c r="F91" s="20" t="inlineStr">
+        <is>
+          <t>dim_SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H91" s="20" t="inlineStr">
+        <is>
+          <t>#,0.0</t>
+        </is>
+      </c>
+      <c r="I91" s="25" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>K-091</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>07 Service</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>Avg Cycle Days</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr"/>
+      <c r="E92" s="16" t="inlineStr">
+        <is>
+          <t>AVERAGE(dim_SalesOrderLine[Days_Order_To_Ship])</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="inlineStr">
+        <is>
+          <t>dim_SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H92" s="13" t="inlineStr">
+        <is>
+          <t>#,0.0</t>
+        </is>
+      </c>
+      <c r="I92" s="18" t="inlineStr">
+        <is>
+          <t>56.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>K-092</t>
+        </is>
+      </c>
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>07 Service</t>
+        </is>
+      </c>
+      <c r="C93" s="21" t="inlineStr">
+        <is>
           <t>P90 Cycle Days</t>
         </is>
       </c>
-      <c r="D89" s="22" t="inlineStr">
+      <c r="D93" s="22" t="inlineStr">
         <is>
           <t>The realistic service promise. Set promise dates from this, not the best case.</t>
         </is>
       </c>
-      <c r="E89" s="23" t="inlineStr">
+      <c r="E93" s="23" t="inlineStr">
         <is>
           <t>PERCENTILE.INC(dim_SalesOrderLine[Days_Order_To_Ship], 0.9)</t>
         </is>
       </c>
-      <c r="F89" s="20" t="inlineStr">
+      <c r="F93" s="20" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G89" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H89" s="20" t="inlineStr">
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H93" s="20" t="inlineStr">
         <is>
           <t>#,0.0</t>
         </is>
       </c>
-      <c r="I89" s="25" t="inlineStr">
-        <is>
-          <t>65.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="71" customHeight="1">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t>K-089</t>
-        </is>
-      </c>
-      <c r="B90" s="13" t="inlineStr">
+      <c r="I93" s="25" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="71" customHeight="1">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>K-093</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>07 Service</t>
         </is>
       </c>
-      <c r="C90" s="14" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr">
         <is>
           <t>On Time Delivery %</t>
         </is>
       </c>
-      <c r="D90" s="15" t="inlineStr">
+      <c r="D94" s="15" t="inlineStr">
         <is>
           <t>Arrivals on or before plan. Computable on 76% of rows.</t>
         </is>
       </c>
-      <c r="E90" s="16" t="inlineStr">
+      <c r="E94" s="16" t="inlineStr">
         <is>
           <t>VAR Base =
     CALCULATE(COUNTROWS(fact_Shipment), NOT ISBLANK(fact_Shipment[Actual_Arrival]))
@@ -5253,88 +5445,88 @@
     DIVIDE(OnTime, Base)</t>
         </is>
       </c>
-      <c r="F90" s="13" t="inlineStr">
+      <c r="F94" s="13" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G90" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H90" s="13" t="inlineStr">
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H94" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I90" s="18" t="inlineStr">
+      <c r="I94" s="18" t="inlineStr">
         <is>
           <t>68.3%</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="26" customHeight="1">
-      <c r="A91" s="19" t="inlineStr">
-        <is>
-          <t>K-090</t>
-        </is>
-      </c>
-      <c r="B91" s="20" t="inlineStr">
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>K-094</t>
+        </is>
+      </c>
+      <c r="B95" s="20" t="inlineStr">
         <is>
           <t>07 Service</t>
         </is>
       </c>
-      <c r="C91" s="21" t="inlineStr">
+      <c r="C95" s="21" t="inlineStr">
         <is>
           <t>Avg Delivery Delay Days</t>
         </is>
       </c>
-      <c r="D91" s="22" t="inlineStr"/>
-      <c r="E91" s="23" t="inlineStr">
+      <c r="D95" s="22" t="inlineStr"/>
+      <c r="E95" s="23" t="inlineStr">
         <is>
           <t>AVERAGE(fact_Shipment[Delivery_Delay_Days])</t>
         </is>
       </c>
-      <c r="F91" s="20" t="inlineStr">
+      <c r="F95" s="20" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G91" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H91" s="20" t="inlineStr">
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H95" s="20" t="inlineStr">
         <is>
           <t>#,0.0</t>
         </is>
       </c>
-      <c r="I91" s="25" t="inlineStr">
+      <c r="I95" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="113" customHeight="1">
-      <c r="A92" s="12" t="inlineStr">
-        <is>
-          <t>K-091</t>
-        </is>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
+    <row r="96" ht="113" customHeight="1">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>K-095</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>07 Service</t>
         </is>
       </c>
-      <c r="C92" s="14" t="inlineStr">
+      <c r="C96" s="14" t="inlineStr">
         <is>
           <t>In Full Rate %</t>
         </is>
       </c>
-      <c r="D92" s="15" t="inlineStr"/>
-      <c r="E92" s="16" t="inlineStr">
+      <c r="D96" s="15" t="inlineStr"/>
+      <c r="E96" s="16" t="inlineStr">
         <is>
           <t>DIVIDE(
     CALCULATE(
@@ -5348,49 +5540,49 @@
 )</t>
         </is>
       </c>
-      <c r="F92" s="13" t="inlineStr">
+      <c r="F96" s="13" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G92" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H92" s="13" t="inlineStr">
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H96" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I92" s="18" t="inlineStr">
+      <c r="I96" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="134" customHeight="1">
-      <c r="A93" s="19" t="inlineStr">
-        <is>
-          <t>K-092</t>
-        </is>
-      </c>
-      <c r="B93" s="20" t="inlineStr">
+    <row r="97" ht="134" customHeight="1">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>K-096</t>
+        </is>
+      </c>
+      <c r="B97" s="20" t="inlineStr">
         <is>
           <t>07 Service</t>
         </is>
       </c>
-      <c r="C93" s="21" t="inlineStr">
+      <c r="C97" s="21" t="inlineStr">
         <is>
           <t>OTIF %</t>
         </is>
       </c>
-      <c r="D93" s="22" t="inlineStr">
+      <c r="D97" s="22" t="inlineStr">
         <is>
           <t>Agree the on-time baseline with the business before publishing this.</t>
         </is>
       </c>
-      <c r="E93" s="23" t="inlineStr">
+      <c r="E97" s="23" t="inlineStr">
         <is>
           <t>VAR Qualified =
     CALCULATE(
@@ -5406,200 +5598,24 @@
     DIVIDE(Qualified, [Order Lines])</t>
         </is>
       </c>
-      <c r="F93" s="20" t="inlineStr">
+      <c r="F97" s="20" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G93" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H93" s="20" t="inlineStr">
+      <c r="G97" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H97" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I93" s="25" t="inlineStr">
+      <c r="I97" s="25" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="26" customHeight="1">
-      <c r="A94" s="12" t="inlineStr">
-        <is>
-          <t>K-093</t>
-        </is>
-      </c>
-      <c r="B94" s="13" t="inlineStr">
-        <is>
-          <t>08 Logistics</t>
-        </is>
-      </c>
-      <c r="C94" s="14" t="inlineStr">
-        <is>
-          <t>Avg MT per Delivery</t>
-        </is>
-      </c>
-      <c r="D94" s="15" t="inlineStr"/>
-      <c r="E94" s="16" t="inlineStr">
-        <is>
-          <t>DIVIDE([Shipped MT], [Deliveries])</t>
-        </is>
-      </c>
-      <c r="F94" s="13" t="inlineStr">
-        <is>
-          <t>fact_Shipment</t>
-        </is>
-      </c>
-      <c r="G94" s="26" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H94" s="13" t="inlineStr">
-        <is>
-          <t>#,0.0</t>
-        </is>
-      </c>
-      <c r="I94" s="18" t="inlineStr">
-        <is>
-          <t>353.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="26" customHeight="1">
-      <c r="A95" s="19" t="inlineStr">
-        <is>
-          <t>K-094</t>
-        </is>
-      </c>
-      <c r="B95" s="20" t="inlineStr">
-        <is>
-          <t>08 Logistics</t>
-        </is>
-      </c>
-      <c r="C95" s="21" t="inlineStr">
-        <is>
-          <t>Avg MT per Trip</t>
-        </is>
-      </c>
-      <c r="D95" s="22" t="inlineStr"/>
-      <c r="E95" s="23" t="inlineStr">
-        <is>
-          <t>DIVIDE([Shipped MT], [Trips])</t>
-        </is>
-      </c>
-      <c r="F95" s="20" t="inlineStr">
-        <is>
-          <t>fact_Shipment</t>
-        </is>
-      </c>
-      <c r="G95" s="27" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H95" s="20" t="inlineStr">
-        <is>
-          <t>#,0.0</t>
-        </is>
-      </c>
-      <c r="I95" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="26" customHeight="1">
-      <c r="A96" s="12" t="inlineStr">
-        <is>
-          <t>K-095</t>
-        </is>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>08 Logistics</t>
-        </is>
-      </c>
-      <c r="C96" s="14" t="inlineStr">
-        <is>
-          <t>Deliveries per Trip</t>
-        </is>
-      </c>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>Consolidation efficiency.</t>
-        </is>
-      </c>
-      <c r="E96" s="16" t="inlineStr">
-        <is>
-          <t>DIVIDE([Deliveries], [Trips])</t>
-        </is>
-      </c>
-      <c r="F96" s="13" t="inlineStr">
-        <is>
-          <t>fact_Shipment</t>
-        </is>
-      </c>
-      <c r="G96" s="26" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H96" s="13" t="inlineStr">
-        <is>
-          <t>#,0.00</t>
-        </is>
-      </c>
-      <c r="I96" s="18" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="26" customHeight="1">
-      <c r="A97" s="19" t="inlineStr">
-        <is>
-          <t>K-096</t>
-        </is>
-      </c>
-      <c r="B97" s="20" t="inlineStr">
-        <is>
-          <t>08 Logistics</t>
-        </is>
-      </c>
-      <c r="C97" s="21" t="inlineStr">
-        <is>
-          <t>Active Carriers</t>
-        </is>
-      </c>
-      <c r="D97" s="22" t="inlineStr"/>
-      <c r="E97" s="23" t="inlineStr">
-        <is>
-          <t>CALCULATE(DISTINCTCOUNT(fact_Shipment[CarrierKey]), fact_Shipment[CarrierKey] &lt;&gt; "-1")</t>
-        </is>
-      </c>
-      <c r="F97" s="20" t="inlineStr">
-        <is>
-          <t>fact_Shipment</t>
-        </is>
-      </c>
-      <c r="G97" s="27" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H97" s="20" t="inlineStr">
-        <is>
-          <t>#,0</t>
-        </is>
-      </c>
-      <c r="I97" s="25" t="inlineStr">
-        <is>
-          <t>173</t>
         </is>
       </c>
     </row>
@@ -5616,13 +5632,13 @@
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Requested MT</t>
+          <t>Avg MT per Delivery</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr"/>
       <c r="E98" s="16" t="inlineStr">
         <is>
-          <t>SUM(fact_Shipment[Requested_MT])</t>
+          <t>DIVIDE([Shipped MT], [Deliveries])</t>
         </is>
       </c>
       <c r="F98" s="13" t="inlineStr">
@@ -5637,12 +5653,12 @@
       </c>
       <c r="H98" s="13" t="inlineStr">
         <is>
-          <t>#,0</t>
+          <t>#,0.0</t>
         </is>
       </c>
       <c r="I98" s="18" t="inlineStr">
         <is>
-          <t>21,464,645</t>
+          <t>353.6</t>
         </is>
       </c>
     </row>
@@ -5659,13 +5675,13 @@
       </c>
       <c r="C99" s="21" t="inlineStr">
         <is>
-          <t>Picked MT</t>
+          <t>Avg MT per Trip</t>
         </is>
       </c>
       <c r="D99" s="22" t="inlineStr"/>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>SUM(fact_Shipment[Picked_MT])</t>
+          <t>DIVIDE([Shipped MT], [Trips])</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
@@ -5680,12 +5696,12 @@
       </c>
       <c r="H99" s="20" t="inlineStr">
         <is>
-          <t>#,0</t>
+          <t>#,0.0</t>
         </is>
       </c>
       <c r="I99" s="25" t="inlineStr">
         <is>
-          <t>21,207,780</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5702,17 +5718,17 @@
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Cancelled MT Logistics</t>
+          <t>Deliveries per Trip</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>Cancellation after picking began — distinct from an order-level cancellation.</t>
+          <t>Consolidation efficiency.</t>
         </is>
       </c>
       <c r="E100" s="16" t="inlineStr">
         <is>
-          <t>SUM(fact_Shipment[Cancelled_MT])</t>
+          <t>DIVIDE([Deliveries], [Trips])</t>
         </is>
       </c>
       <c r="F100" s="13" t="inlineStr">
@@ -5727,12 +5743,12 @@
       </c>
       <c r="H100" s="13" t="inlineStr">
         <is>
-          <t>#,0</t>
+          <t>#,0.00</t>
         </is>
       </c>
       <c r="I100" s="18" t="inlineStr">
         <is>
-          <t>451,304</t>
+          <t>1.20</t>
         </is>
       </c>
     </row>
@@ -5749,13 +5765,13 @@
       </c>
       <c r="C101" s="21" t="inlineStr">
         <is>
-          <t>Pick Completion %</t>
+          <t>Active Carriers</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr"/>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>DIVIDE([Picked MT], [Requested MT])</t>
+          <t>CALCULATE(DISTINCTCOUNT(fact_Shipment[CarrierKey]), fact_Shipment[CarrierKey] &lt;&gt; "-1")</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
@@ -5770,12 +5786,12 @@
       </c>
       <c r="H101" s="20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>#,0</t>
         </is>
       </c>
       <c r="I101" s="25" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>173</t>
         </is>
       </c>
     </row>
@@ -5792,58 +5808,234 @@
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Ship Completion %</t>
+          <t>Requested MT</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr"/>
       <c r="E102" s="16" t="inlineStr">
         <is>
+          <t>SUM(fact_Shipment[Requested_MT])</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="inlineStr">
+        <is>
+          <t>fact_Shipment</t>
+        </is>
+      </c>
+      <c r="G102" s="26" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H102" s="13" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I102" s="18" t="inlineStr">
+        <is>
+          <t>21,464,645</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="26" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>K-102</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="inlineStr">
+        <is>
+          <t>08 Logistics</t>
+        </is>
+      </c>
+      <c r="C103" s="21" t="inlineStr">
+        <is>
+          <t>Picked MT</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="inlineStr"/>
+      <c r="E103" s="23" t="inlineStr">
+        <is>
+          <t>SUM(fact_Shipment[Picked_MT])</t>
+        </is>
+      </c>
+      <c r="F103" s="20" t="inlineStr">
+        <is>
+          <t>fact_Shipment</t>
+        </is>
+      </c>
+      <c r="G103" s="27" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H103" s="20" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I103" s="25" t="inlineStr">
+        <is>
+          <t>21,207,780</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="26" customHeight="1">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>K-103</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>08 Logistics</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>Cancelled MT Logistics</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>Cancellation after picking began — distinct from an order-level cancellation.</t>
+        </is>
+      </c>
+      <c r="E104" s="16" t="inlineStr">
+        <is>
+          <t>SUM(fact_Shipment[Cancelled_MT])</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="inlineStr">
+        <is>
+          <t>fact_Shipment</t>
+        </is>
+      </c>
+      <c r="G104" s="26" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H104" s="13" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I104" s="18" t="inlineStr">
+        <is>
+          <t>451,304</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="26" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>K-104</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="inlineStr">
+        <is>
+          <t>08 Logistics</t>
+        </is>
+      </c>
+      <c r="C105" s="21" t="inlineStr">
+        <is>
+          <t>Pick Completion %</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr"/>
+      <c r="E105" s="23" t="inlineStr">
+        <is>
+          <t>DIVIDE([Picked MT], [Requested MT])</t>
+        </is>
+      </c>
+      <c r="F105" s="20" t="inlineStr">
+        <is>
+          <t>fact_Shipment</t>
+        </is>
+      </c>
+      <c r="G105" s="27" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H105" s="20" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I105" s="25" t="inlineStr">
+        <is>
+          <t>98.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="26" customHeight="1">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>K-105</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>08 Logistics</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>Ship Completion %</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="inlineStr"/>
+      <c r="E106" s="16" t="inlineStr">
+        <is>
           <t>DIVIDE([Shipped MT], [Picked MT])</t>
         </is>
       </c>
-      <c r="F102" s="13" t="inlineStr">
+      <c r="F106" s="13" t="inlineStr">
         <is>
           <t>fact_Shipment</t>
         </is>
       </c>
-      <c r="G102" s="26" t="inlineStr">
+      <c r="G106" s="26" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H102" s="13" t="inlineStr">
+      <c r="H106" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I102" s="18" t="inlineStr">
+      <c r="I106" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="50" customHeight="1">
-      <c r="A103" s="19" t="inlineStr">
-        <is>
-          <t>K-102</t>
-        </is>
-      </c>
-      <c r="B103" s="20" t="inlineStr">
+    <row r="107" ht="50" customHeight="1">
+      <c r="A107" s="19" t="inlineStr">
+        <is>
+          <t>K-106</t>
+        </is>
+      </c>
+      <c r="B107" s="20" t="inlineStr">
         <is>
           <t>08 Logistics</t>
         </is>
       </c>
-      <c r="C103" s="21" t="inlineStr">
+      <c r="C107" s="21" t="inlineStr">
         <is>
           <t>Packaging Overhead %</t>
         </is>
       </c>
-      <c r="D103" s="22" t="inlineStr">
+      <c r="D107" s="22" t="inlineStr">
         <is>
           <t>Freight paid on non-product weight.</t>
         </is>
       </c>
-      <c r="E103" s="23" t="inlineStr">
+      <c r="E107" s="23" t="inlineStr">
         <is>
           <t>DIVIDE(
     SUM(fact_Shipment[Gross_Weight_MT]) - SUM(fact_Shipment[Net_Weight_MT]),
@@ -5851,45 +6043,45 @@
 )</t>
         </is>
       </c>
-      <c r="F103" s="20" t="inlineStr">
+      <c r="F107" s="20" t="inlineStr">
         <is>
           <t>fact_Shipment</t>
         </is>
       </c>
-      <c r="G103" s="27" t="inlineStr">
+      <c r="G107" s="27" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H103" s="20" t="inlineStr">
+      <c r="H107" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I103" s="25" t="inlineStr">
+      <c r="I107" s="25" t="inlineStr">
         <is>
           <t>3.27%</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="50" customHeight="1">
-      <c r="A104" s="12" t="inlineStr">
-        <is>
-          <t>K-103</t>
-        </is>
-      </c>
-      <c r="B104" s="13" t="inlineStr">
+    <row r="108" ht="50" customHeight="1">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>K-107</t>
+        </is>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
         <is>
           <t>08 Logistics</t>
         </is>
       </c>
-      <c r="C104" s="14" t="inlineStr">
+      <c r="C108" s="14" t="inlineStr">
         <is>
           <t>Export Share %</t>
         </is>
       </c>
-      <c r="D104" s="15" t="inlineStr"/>
-      <c r="E104" s="16" t="inlineStr">
+      <c r="D108" s="15" t="inlineStr"/>
+      <c r="E108" s="16" t="inlineStr">
         <is>
           <t>DIVIDE(
     CALCULATE(COUNTROWS(fact_Shipment), fact_Shipment[Is_Export] = TRUE()),
@@ -5897,135 +6089,135 @@
 )</t>
         </is>
       </c>
-      <c r="F104" s="13" t="inlineStr">
+      <c r="F108" s="13" t="inlineStr">
         <is>
           <t>fact_Shipment</t>
         </is>
       </c>
-      <c r="G104" s="26" t="inlineStr">
+      <c r="G108" s="26" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H104" s="13" t="inlineStr">
+      <c r="H108" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I104" s="18" t="inlineStr">
+      <c r="I108" s="18" t="inlineStr">
         <is>
           <t>56.4%</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="26" customHeight="1">
-      <c r="A105" s="19" t="inlineStr">
-        <is>
-          <t>K-104</t>
-        </is>
-      </c>
-      <c r="B105" s="20" t="inlineStr">
+    <row r="109" ht="26" customHeight="1">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>K-108</t>
+        </is>
+      </c>
+      <c r="B109" s="20" t="inlineStr">
         <is>
           <t>08 Logistics</t>
         </is>
       </c>
-      <c r="C105" s="21" t="inlineStr">
+      <c r="C109" s="21" t="inlineStr">
         <is>
           <t>Countries Served</t>
         </is>
       </c>
-      <c r="D105" s="22" t="inlineStr"/>
-      <c r="E105" s="23" t="inlineStr">
+      <c r="D109" s="22" t="inlineStr"/>
+      <c r="E109" s="23" t="inlineStr">
         <is>
           <t>DISTINCTCOUNT(fact_Shipment[Ship_To_Country])</t>
         </is>
       </c>
-      <c r="F105" s="20" t="inlineStr">
+      <c r="F109" s="20" t="inlineStr">
         <is>
           <t>fact_Shipment</t>
         </is>
       </c>
-      <c r="G105" s="27" t="inlineStr">
+      <c r="G109" s="27" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H105" s="20" t="inlineStr">
+      <c r="H109" s="20" t="inlineStr">
         <is>
           <t>#,0</t>
         </is>
       </c>
-      <c r="I105" s="25" t="inlineStr">
+      <c r="I109" s="25" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="26" customHeight="1">
-      <c r="A106" s="12" t="inlineStr">
-        <is>
-          <t>K-105</t>
-        </is>
-      </c>
-      <c r="B106" s="13" t="inlineStr">
+    <row r="110" ht="26" customHeight="1">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>K-109</t>
+        </is>
+      </c>
+      <c r="B110" s="13" t="inlineStr">
         <is>
           <t>08 Logistics</t>
         </is>
       </c>
-      <c r="C106" s="14" t="inlineStr">
+      <c r="C110" s="14" t="inlineStr">
         <is>
           <t>Carrier Volume Share %</t>
         </is>
       </c>
-      <c r="D106" s="15" t="inlineStr"/>
-      <c r="E106" s="16" t="inlineStr">
+      <c r="D110" s="15" t="inlineStr"/>
+      <c r="E110" s="16" t="inlineStr">
         <is>
           <t>DIVIDE([Shipped MT], CALCULATE([Shipped MT], ALL(dim_Carrier)))</t>
         </is>
       </c>
-      <c r="F106" s="13" t="inlineStr">
+      <c r="F110" s="13" t="inlineStr">
         <is>
           <t>fact_Shipment</t>
         </is>
       </c>
-      <c r="G106" s="26" t="inlineStr">
+      <c r="G110" s="26" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H106" s="13" t="inlineStr">
+      <c r="H110" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I106" s="18" t="inlineStr">
+      <c r="I110" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="50" customHeight="1">
-      <c r="A107" s="19" t="inlineStr">
-        <is>
-          <t>K-106</t>
-        </is>
-      </c>
-      <c r="B107" s="20" t="inlineStr">
+    <row r="111" ht="50" customHeight="1">
+      <c r="A111" s="19" t="inlineStr">
+        <is>
+          <t>K-110</t>
+        </is>
+      </c>
+      <c r="B111" s="20" t="inlineStr">
         <is>
           <t>08 Logistics</t>
         </is>
       </c>
-      <c r="C107" s="21" t="inlineStr">
+      <c r="C111" s="21" t="inlineStr">
         <is>
           <t>Missing Carrier %</t>
         </is>
       </c>
-      <c r="D107" s="22" t="inlineStr">
+      <c r="D111" s="22" t="inlineStr">
         <is>
           <t>Blind spot in the carrier scorecard.</t>
         </is>
       </c>
-      <c r="E107" s="23" t="inlineStr">
+      <c r="E111" s="23" t="inlineStr">
         <is>
           <t>DIVIDE(
     CALCULATE(COUNTROWS(fact_Shipment), fact_Shipment[CarrierKey] = "-1"),
@@ -6033,49 +6225,49 @@
 )</t>
         </is>
       </c>
-      <c r="F107" s="20" t="inlineStr">
+      <c r="F111" s="20" t="inlineStr">
         <is>
           <t>fact_Shipment</t>
         </is>
       </c>
-      <c r="G107" s="27" t="inlineStr">
+      <c r="G111" s="27" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H107" s="20" t="inlineStr">
+      <c r="H111" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I107" s="25" t="inlineStr">
+      <c r="I111" s="25" t="inlineStr">
         <is>
           <t>23.5%</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="123.5" customHeight="1">
-      <c r="A108" s="12" t="inlineStr">
-        <is>
-          <t>K-107</t>
-        </is>
-      </c>
-      <c r="B108" s="13" t="inlineStr">
+    <row r="112" ht="123.5" customHeight="1">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>K-111</t>
+        </is>
+      </c>
+      <c r="B112" s="13" t="inlineStr">
         <is>
           <t>08 Logistics</t>
         </is>
       </c>
-      <c r="C108" s="14" t="inlineStr">
+      <c r="C112" s="14" t="inlineStr">
         <is>
           <t>Tolerance Breach %</t>
         </is>
       </c>
-      <c r="D108" s="15" t="inlineStr">
+      <c r="D112" s="15" t="inlineStr">
         <is>
           <t>Tolerance columns are ~100% populated, so this is reliable.</t>
         </is>
       </c>
-      <c r="E108" s="16" t="inlineStr">
+      <c r="E112" s="16" t="inlineStr">
         <is>
           <t>DIVIDE(
     CALCULATE(
@@ -6090,178 +6282,178 @@
 )</t>
         </is>
       </c>
-      <c r="F108" s="13" t="inlineStr">
+      <c r="F112" s="13" t="inlineStr">
         <is>
           <t>fact_Shipment</t>
         </is>
       </c>
-      <c r="G108" s="26" t="inlineStr">
+      <c r="G112" s="26" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H108" s="13" t="inlineStr">
+      <c r="H112" s="13" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="I108" s="18" t="inlineStr">
+      <c r="I112" s="18" t="inlineStr">
         <is>
           <t>0.53%</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="26" customHeight="1">
-      <c r="A109" s="19" t="inlineStr">
-        <is>
-          <t>K-108</t>
-        </is>
-      </c>
-      <c r="B109" s="20" t="inlineStr">
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="19" t="inlineStr">
+        <is>
+          <t>K-112</t>
+        </is>
+      </c>
+      <c r="B113" s="20" t="inlineStr">
         <is>
           <t>09 Returns &amp; Credits</t>
         </is>
       </c>
-      <c r="C109" s="21" t="inlineStr">
+      <c r="C113" s="21" t="inlineStr">
         <is>
           <t>Return Lines</t>
         </is>
       </c>
-      <c r="D109" s="22" t="inlineStr"/>
-      <c r="E109" s="23" t="inlineStr">
+      <c r="D113" s="22" t="inlineStr"/>
+      <c r="E113" s="23" t="inlineStr">
         <is>
           <t>CALCULATE([Order Lines], dim_SalesOrderLine[Is_Return] = TRUE())</t>
         </is>
       </c>
-      <c r="F109" s="20" t="inlineStr">
+      <c r="F113" s="20" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G109" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H109" s="20" t="inlineStr">
+      <c r="G113" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H113" s="20" t="inlineStr">
         <is>
           <t>#,0</t>
         </is>
       </c>
-      <c r="I109" s="25" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="26" customHeight="1">
-      <c r="A110" s="12" t="inlineStr">
-        <is>
-          <t>K-109</t>
-        </is>
-      </c>
-      <c r="B110" s="13" t="inlineStr">
+      <c r="I113" s="25" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="26" customHeight="1">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>K-113</t>
+        </is>
+      </c>
+      <c r="B114" s="13" t="inlineStr">
         <is>
           <t>09 Returns &amp; Credits</t>
         </is>
       </c>
-      <c r="C110" s="14" t="inlineStr">
+      <c r="C114" s="14" t="inlineStr">
         <is>
           <t>Return Rate %</t>
         </is>
       </c>
-      <c r="D110" s="15" t="inlineStr">
+      <c r="D114" s="15" t="inlineStr">
         <is>
           <t>Label this Credit Note Rate externally. Most returns are billing corrections, not goods coming back.</t>
         </is>
       </c>
-      <c r="E110" s="16" t="inlineStr">
+      <c r="E114" s="16" t="inlineStr">
         <is>
           <t>DIVIDE([Return Lines], [Order Lines])</t>
         </is>
       </c>
-      <c r="F110" s="13" t="inlineStr">
+      <c r="F114" s="13" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G110" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H110" s="13" t="inlineStr">
+      <c r="G114" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H114" s="13" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="I110" s="18" t="inlineStr">
-        <is>
-          <t>0.89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="26" customHeight="1">
-      <c r="A111" s="19" t="inlineStr">
-        <is>
-          <t>K-110</t>
-        </is>
-      </c>
-      <c r="B111" s="20" t="inlineStr">
+      <c r="I114" s="18" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="26" customHeight="1">
+      <c r="A115" s="19" t="inlineStr">
+        <is>
+          <t>K-114</t>
+        </is>
+      </c>
+      <c r="B115" s="20" t="inlineStr">
         <is>
           <t>09 Returns &amp; Credits</t>
         </is>
       </c>
-      <c r="C111" s="21" t="inlineStr">
+      <c r="C115" s="21" t="inlineStr">
         <is>
           <t>Returned MT</t>
         </is>
       </c>
-      <c r="D111" s="22" t="inlineStr"/>
-      <c r="E111" s="23" t="inlineStr">
+      <c r="D115" s="22" t="inlineStr"/>
+      <c r="E115" s="23" t="inlineStr">
         <is>
           <t>ABS(CALCULATE([Ordered MT], dim_SalesOrderLine[Is_Return] = TRUE()))</t>
         </is>
       </c>
-      <c r="F111" s="20" t="inlineStr">
+      <c r="F115" s="20" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G111" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H111" s="20" t="inlineStr">
+      <c r="G115" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H115" s="20" t="inlineStr">
         <is>
           <t>#,0</t>
         </is>
       </c>
-      <c r="I111" s="25" t="inlineStr">
-        <is>
-          <t>539,051</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="50" customHeight="1">
-      <c r="A112" s="12" t="inlineStr">
-        <is>
-          <t>K-111</t>
-        </is>
-      </c>
-      <c r="B112" s="13" t="inlineStr">
+      <c r="I115" s="25" t="inlineStr">
+        <is>
+          <t>~500,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="50" customHeight="1">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>K-115</t>
+        </is>
+      </c>
+      <c r="B116" s="13" t="inlineStr">
         <is>
           <t>09 Returns &amp; Credits</t>
         </is>
       </c>
-      <c r="C112" s="14" t="inlineStr">
+      <c r="C116" s="14" t="inlineStr">
         <is>
           <t>Return Rate Volume %</t>
         </is>
       </c>
-      <c r="D112" s="15" t="inlineStr"/>
-      <c r="E112" s="16" t="inlineStr">
+      <c r="D116" s="15" t="inlineStr"/>
+      <c r="E116" s="16" t="inlineStr">
         <is>
           <t>DIVIDE(
     [Returned MT],
@@ -6269,208 +6461,24 @@
 )</t>
         </is>
       </c>
-      <c r="F112" s="13" t="inlineStr">
+      <c r="F116" s="13" t="inlineStr">
         <is>
           <t>dim_SalesOrderLine</t>
         </is>
       </c>
-      <c r="G112" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H112" s="13" t="inlineStr">
+      <c r="G116" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H116" s="13" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="I112" s="18" t="inlineStr">
-        <is>
-          <t>2.10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="26" customHeight="1">
-      <c r="A113" s="19" t="inlineStr">
-        <is>
-          <t>K-112</t>
-        </is>
-      </c>
-      <c r="B113" s="20" t="inlineStr">
-        <is>
-          <t>09 Returns &amp; Credits</t>
-        </is>
-      </c>
-      <c r="C113" s="21" t="inlineStr">
-        <is>
-          <t>Physical Return Lines</t>
-        </is>
-      </c>
-      <c r="D113" s="22" t="inlineStr">
-        <is>
-          <t>Genuinely rejected inventory. 38 of 608 returns.</t>
-        </is>
-      </c>
-      <c r="E113" s="23" t="inlineStr">
-        <is>
-          <t>CALCULATE([Order Lines], dim_ReturnReason[Is_Physical_Return] = TRUE())</t>
-        </is>
-      </c>
-      <c r="F113" s="20" t="inlineStr">
-        <is>
-          <t>dim_SalesOrderLine</t>
-        </is>
-      </c>
-      <c r="G113" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H113" s="20" t="inlineStr">
-        <is>
-          <t>#,0</t>
-        </is>
-      </c>
-      <c r="I113" s="25" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="26" customHeight="1">
-      <c r="A114" s="12" t="inlineStr">
-        <is>
-          <t>K-113</t>
-        </is>
-      </c>
-      <c r="B114" s="13" t="inlineStr">
-        <is>
-          <t>09 Returns &amp; Credits</t>
-        </is>
-      </c>
-      <c r="C114" s="14" t="inlineStr">
-        <is>
-          <t>Physical Return Rate %</t>
-        </is>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>The true product-quality metric.</t>
-        </is>
-      </c>
-      <c r="E114" s="16" t="inlineStr">
-        <is>
-          <t>DIVIDE([Physical Return Lines], [Order Lines])</t>
-        </is>
-      </c>
-      <c r="F114" s="13" t="inlineStr">
-        <is>
-          <t>dim_SalesOrderLine</t>
-        </is>
-      </c>
-      <c r="G114" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H114" s="13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I114" s="18" t="inlineStr">
-        <is>
-          <t>0.06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="26" customHeight="1">
-      <c r="A115" s="19" t="inlineStr">
-        <is>
-          <t>K-114</t>
-        </is>
-      </c>
-      <c r="B115" s="20" t="inlineStr">
-        <is>
-          <t>09 Returns &amp; Credits</t>
-        </is>
-      </c>
-      <c r="C115" s="21" t="inlineStr">
-        <is>
-          <t>Commercial Adjustment Lines</t>
-        </is>
-      </c>
-      <c r="D115" s="22" t="inlineStr"/>
-      <c r="E115" s="23" t="inlineStr">
-        <is>
-          <t>CALCULATE([Return Lines], dim_ReturnReason[Reason_Group] = "Commercial adjustment")</t>
-        </is>
-      </c>
-      <c r="F115" s="20" t="inlineStr">
-        <is>
-          <t>dim_SalesOrderLine</t>
-        </is>
-      </c>
-      <c r="G115" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H115" s="20" t="inlineStr">
-        <is>
-          <t>#,0</t>
-        </is>
-      </c>
-      <c r="I115" s="25" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="26" customHeight="1">
-      <c r="A116" s="12" t="inlineStr">
-        <is>
-          <t>K-115</t>
-        </is>
-      </c>
-      <c r="B116" s="13" t="inlineStr">
-        <is>
-          <t>09 Returns &amp; Credits</t>
-        </is>
-      </c>
-      <c r="C116" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Adjustment Share %</t>
-        </is>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>High share means pricing accuracy, not quality, is the problem.</t>
-        </is>
-      </c>
-      <c r="E116" s="16" t="inlineStr">
-        <is>
-          <t>DIVIDE([Commercial Adjustment Lines], [Return Lines])</t>
-        </is>
-      </c>
-      <c r="F116" s="13" t="inlineStr">
-        <is>
-          <t>dim_SalesOrderLine</t>
-        </is>
-      </c>
-      <c r="G116" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H116" s="13" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="I116" s="18" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>~2.0%</t>
         </is>
       </c>
     </row>
@@ -6482,28 +6490,32 @@
       </c>
       <c r="B117" s="20" t="inlineStr">
         <is>
-          <t>10 Customer &amp; Product</t>
+          <t>09 Returns &amp; Credits</t>
         </is>
       </c>
       <c r="C117" s="21" t="inlineStr">
         <is>
-          <t>Active Customers</t>
-        </is>
-      </c>
-      <c r="D117" s="22" t="inlineStr"/>
+          <t>Physical Return Lines</t>
+        </is>
+      </c>
+      <c r="D117" s="22" t="inlineStr">
+        <is>
+          <t>Genuinely rejected inventory. 38 of 608 returns.</t>
+        </is>
+      </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>CALCULATE(DISTINCTCOUNT(dim_SalesOrderLine[CustomerKey]), [Net Revenue USD] &lt;&gt; 0)</t>
+          <t>CALCULATE([Order Lines], dim_ReturnReason[Is_Physical_Return] = TRUE())</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
         <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="G117" s="27" t="inlineStr">
-        <is>
-          <t>Standard</t>
+          <t>dim_SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="G117" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="H117" s="20" t="inlineStr">
@@ -6513,7 +6525,7 @@
       </c>
       <c r="I117" s="25" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -6525,38 +6537,42 @@
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>10 Customer &amp; Product</t>
+          <t>09 Returns &amp; Credits</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Revenue per Customer</t>
-        </is>
-      </c>
-      <c r="D118" s="15" t="inlineStr"/>
+          <t>Physical Return Rate %</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>The true product-quality metric.</t>
+        </is>
+      </c>
       <c r="E118" s="16" t="inlineStr">
         <is>
-          <t>DIVIDE([Net Revenue USD], [Active Customers])</t>
+          <t>DIVIDE([Physical Return Lines], [Order Lines])</t>
         </is>
       </c>
       <c r="F118" s="13" t="inlineStr">
         <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="G118" s="26" t="inlineStr">
-        <is>
-          <t>Standard</t>
+          <t>dim_SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="G118" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
         <is>
-          <t>\$#,0</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="I118" s="18" t="inlineStr">
         <is>
-          <t>$20.6m</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -6568,28 +6584,28 @@
       </c>
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>10 Customer &amp; Product</t>
+          <t>09 Returns &amp; Credits</t>
         </is>
       </c>
       <c r="C119" s="21" t="inlineStr">
         <is>
-          <t>Active Products</t>
+          <t>Commercial Adjustment Lines</t>
         </is>
       </c>
       <c r="D119" s="22" t="inlineStr"/>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>DISTINCTCOUNT(dim_SalesOrderLine[ProductKey])</t>
+          <t>CALCULATE([Return Lines], dim_ReturnReason[Reason_Group] = "Commercial adjustment")</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
         <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="G119" s="27" t="inlineStr">
-        <is>
-          <t>Standard</t>
+          <t>dim_SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="G119" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="H119" s="20" t="inlineStr">
@@ -6599,7 +6615,7 @@
       </c>
       <c r="I119" s="25" t="inlineStr">
         <is>
-          <t>1,722</t>
+          <t>~170</t>
         </is>
       </c>
     </row>
@@ -6611,59 +6627,235 @@
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
+          <t>09 Returns &amp; Credits</t>
+        </is>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Adjustment Share %</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>High share means pricing accuracy, not quality, is the problem.</t>
+        </is>
+      </c>
+      <c r="E120" s="16" t="inlineStr">
+        <is>
+          <t>DIVIDE([Commercial Adjustment Lines], [Return Lines])</t>
+        </is>
+      </c>
+      <c r="F120" s="13" t="inlineStr">
+        <is>
+          <t>dim_SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="G120" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H120" s="13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I120" s="18" t="inlineStr">
+        <is>
+          <t>29.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="26" customHeight="1">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>K-120</t>
+        </is>
+      </c>
+      <c r="B121" s="20" t="inlineStr">
+        <is>
           <t>10 Customer &amp; Product</t>
         </is>
       </c>
-      <c r="C120" s="14" t="inlineStr">
-        <is>
-          <t>Customer Revenue Rank</t>
-        </is>
-      </c>
-      <c r="D120" s="15" t="inlineStr"/>
-      <c r="E120" s="16" t="inlineStr">
-        <is>
-          <t>RANKX(ALL(dim_Customer[CustomerKey]), [Net Revenue USD], , DESC, DENSE)</t>
-        </is>
-      </c>
-      <c r="F120" s="13" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="G120" s="26" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H120" s="13" t="inlineStr">
-        <is>
-          <t>#,0</t>
-        </is>
-      </c>
-      <c r="I120" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="71" customHeight="1">
-      <c r="A121" s="19" t="inlineStr">
-        <is>
-          <t>K-120</t>
-        </is>
-      </c>
-      <c r="B121" s="20" t="inlineStr">
-        <is>
-          <t>10 Customer &amp; Product</t>
-        </is>
-      </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>Top 10 Customer Share %</t>
+          <t>Active Customers</t>
         </is>
       </c>
       <c r="D121" s="22" t="inlineStr"/>
       <c r="E121" s="23" t="inlineStr">
+        <is>
+          <t>CALCULATE(DISTINCTCOUNT(dim_SalesOrderLine[CustomerKey]), [Net Revenue USD] &lt;&gt; 0)</t>
+        </is>
+      </c>
+      <c r="F121" s="20" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G121" s="27" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H121" s="20" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I121" s="25" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="26" customHeight="1">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>K-121</t>
+        </is>
+      </c>
+      <c r="B122" s="13" t="inlineStr">
+        <is>
+          <t>10 Customer &amp; Product</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>Revenue per Customer</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr"/>
+      <c r="E122" s="16" t="inlineStr">
+        <is>
+          <t>DIVIDE([Net Revenue USD], [Active Customers])</t>
+        </is>
+      </c>
+      <c r="F122" s="13" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G122" s="26" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H122" s="13" t="inlineStr">
+        <is>
+          <t>\$#,0</t>
+        </is>
+      </c>
+      <c r="I122" s="18" t="inlineStr">
+        <is>
+          <t>$20.6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="26" customHeight="1">
+      <c r="A123" s="19" t="inlineStr">
+        <is>
+          <t>K-122</t>
+        </is>
+      </c>
+      <c r="B123" s="20" t="inlineStr">
+        <is>
+          <t>10 Customer &amp; Product</t>
+        </is>
+      </c>
+      <c r="C123" s="21" t="inlineStr">
+        <is>
+          <t>Active Products</t>
+        </is>
+      </c>
+      <c r="D123" s="22" t="inlineStr"/>
+      <c r="E123" s="23" t="inlineStr">
+        <is>
+          <t>DISTINCTCOUNT(dim_SalesOrderLine[ProductKey])</t>
+        </is>
+      </c>
+      <c r="F123" s="20" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G123" s="27" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H123" s="20" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I123" s="25" t="inlineStr">
+        <is>
+          <t>1,726</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="26" customHeight="1">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>K-123</t>
+        </is>
+      </c>
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>10 Customer &amp; Product</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>Customer Revenue Rank</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="inlineStr"/>
+      <c r="E124" s="16" t="inlineStr">
+        <is>
+          <t>RANKX(ALL(dim_Customer[CustomerKey]), [Net Revenue USD], , DESC, DENSE)</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="G124" s="26" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H124" s="13" t="inlineStr">
+        <is>
+          <t>#,0</t>
+        </is>
+      </c>
+      <c r="I124" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="71" customHeight="1">
+      <c r="A125" s="19" t="inlineStr">
+        <is>
+          <t>K-124</t>
+        </is>
+      </c>
+      <c r="B125" s="20" t="inlineStr">
+        <is>
+          <t>10 Customer &amp; Product</t>
+        </is>
+      </c>
+      <c r="C125" s="21" t="inlineStr">
+        <is>
+          <t>Top 10 Customer Share %</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="inlineStr"/>
+      <c r="E125" s="23" t="inlineStr">
         <is>
           <t>VAR T = TOPN(10, ALL(dim_Customer[CustomerKey]), [Net Revenue USD], DESC)
 RETURN
@@ -6673,45 +6865,45 @@
     )</t>
         </is>
       </c>
-      <c r="F121" s="20" t="inlineStr">
+      <c r="F125" s="20" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G121" s="27" t="inlineStr">
+      <c r="G125" s="27" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H121" s="20" t="inlineStr">
+      <c r="H125" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I121" s="25" t="inlineStr">
+      <c r="I125" s="25" t="inlineStr">
         <is>
           <t>41.4%</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="71" customHeight="1">
-      <c r="A122" s="12" t="inlineStr">
-        <is>
-          <t>K-121</t>
-        </is>
-      </c>
-      <c r="B122" s="13" t="inlineStr">
+    <row r="126" ht="71" customHeight="1">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>K-125</t>
+        </is>
+      </c>
+      <c r="B126" s="13" t="inlineStr">
         <is>
           <t>10 Customer &amp; Product</t>
         </is>
       </c>
-      <c r="C122" s="14" t="inlineStr">
+      <c r="C126" s="14" t="inlineStr">
         <is>
           <t>Top 20 Customer Share %</t>
         </is>
       </c>
-      <c r="D122" s="15" t="inlineStr"/>
-      <c r="E122" s="16" t="inlineStr">
+      <c r="D126" s="15" t="inlineStr"/>
+      <c r="E126" s="16" t="inlineStr">
         <is>
           <t>VAR T = TOPN(20, ALL(dim_Customer[CustomerKey]), [Net Revenue USD], DESC)
 RETURN
@@ -6721,49 +6913,49 @@
     )</t>
         </is>
       </c>
-      <c r="F122" s="13" t="inlineStr">
+      <c r="F126" s="13" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G122" s="26" t="inlineStr">
+      <c r="G126" s="26" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H122" s="13" t="inlineStr">
+      <c r="H126" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I122" s="18" t="inlineStr">
+      <c r="I126" s="18" t="inlineStr">
         <is>
           <t>51.5%</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="81.5" customHeight="1">
-      <c r="A123" s="19" t="inlineStr">
-        <is>
-          <t>K-122</t>
-        </is>
-      </c>
-      <c r="B123" s="20" t="inlineStr">
+    <row r="127" ht="81.5" customHeight="1">
+      <c r="A127" s="19" t="inlineStr">
+        <is>
+          <t>K-126</t>
+        </is>
+      </c>
+      <c r="B127" s="20" t="inlineStr">
         <is>
           <t>10 Customer &amp; Product</t>
         </is>
       </c>
-      <c r="C123" s="21" t="inlineStr">
+      <c r="C127" s="21" t="inlineStr">
         <is>
           <t>Customer HHI</t>
         </is>
       </c>
-      <c r="D123" s="22" t="inlineStr">
+      <c r="D127" s="22" t="inlineStr">
         <is>
           <t>Herfindahl index. Below 1,500 is unconcentrated.</t>
         </is>
       </c>
-      <c r="E123" s="23" t="inlineStr">
+      <c r="E127" s="23" t="inlineStr">
         <is>
           <t>SUMX(
     VALUES(dim_Customer[CustomerKey]),
@@ -6774,49 +6966,49 @@
 )</t>
         </is>
       </c>
-      <c r="F123" s="20" t="inlineStr">
+      <c r="F127" s="20" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G123" s="27" t="inlineStr">
+      <c r="G127" s="27" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H123" s="20" t="inlineStr">
+      <c r="H127" s="20" t="inlineStr">
         <is>
           <t>#,0</t>
         </is>
       </c>
-      <c r="I123" s="25" t="inlineStr">
+      <c r="I127" s="25" t="inlineStr">
         <is>
           <t>397</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="102.5" customHeight="1">
-      <c r="A124" s="12" t="inlineStr">
-        <is>
-          <t>K-123</t>
-        </is>
-      </c>
-      <c r="B124" s="13" t="inlineStr">
+    <row r="128" ht="102.5" customHeight="1">
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>K-127</t>
+        </is>
+      </c>
+      <c r="B128" s="13" t="inlineStr">
         <is>
           <t>10 Customer &amp; Product</t>
         </is>
       </c>
-      <c r="C124" s="14" t="inlineStr">
+      <c r="C128" s="14" t="inlineStr">
         <is>
           <t>Cumulative Revenue Share %</t>
         </is>
       </c>
-      <c r="D124" s="15" t="inlineStr">
+      <c r="D128" s="15" t="inlineStr">
         <is>
           <t>Drives the Pareto curve.</t>
         </is>
       </c>
-      <c r="E124" s="16" t="inlineStr">
+      <c r="E128" s="16" t="inlineStr">
         <is>
           <t>VAR CurrentRank = [Customer Revenue Rank]
 VAR Total       = CALCULATE([Net Revenue USD], ALL(dim_Customer))
@@ -6829,45 +7021,45 @@
     DIVIDE(Running, Total)</t>
         </is>
       </c>
-      <c r="F124" s="13" t="inlineStr">
+      <c r="F128" s="13" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G124" s="26" t="inlineStr">
+      <c r="G128" s="26" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H124" s="13" t="inlineStr">
+      <c r="H128" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I124" s="18" t="inlineStr">
+      <c r="I128" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="71" customHeight="1">
-      <c r="A125" s="19" t="inlineStr">
-        <is>
-          <t>K-124</t>
-        </is>
-      </c>
-      <c r="B125" s="20" t="inlineStr">
+    <row r="129" ht="71" customHeight="1">
+      <c r="A129" s="19" t="inlineStr">
+        <is>
+          <t>K-128</t>
+        </is>
+      </c>
+      <c r="B129" s="20" t="inlineStr">
         <is>
           <t>10 Customer &amp; Product</t>
         </is>
       </c>
-      <c r="C125" s="21" t="inlineStr">
+      <c r="C129" s="21" t="inlineStr">
         <is>
           <t>Top 10 Product Share %</t>
         </is>
       </c>
-      <c r="D125" s="22" t="inlineStr"/>
-      <c r="E125" s="23" t="inlineStr">
+      <c r="D129" s="22" t="inlineStr"/>
+      <c r="E129" s="23" t="inlineStr">
         <is>
           <t>VAR T = TOPN(10, ALL(dim_Product[ProductKey]), [Net Revenue USD], DESC)
 RETURN
@@ -6877,49 +7069,49 @@
     )</t>
         </is>
       </c>
-      <c r="F125" s="20" t="inlineStr">
+      <c r="F129" s="20" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G125" s="27" t="inlineStr">
+      <c r="G129" s="27" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H125" s="20" t="inlineStr">
+      <c r="H129" s="20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I125" s="25" t="inlineStr">
+      <c r="I129" s="25" t="inlineStr">
         <is>
           <t>37.8%</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60.5" customHeight="1">
-      <c r="A126" s="12" t="inlineStr">
-        <is>
-          <t>K-125</t>
-        </is>
-      </c>
-      <c r="B126" s="13" t="inlineStr">
+    <row r="130" ht="60.5" customHeight="1">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>K-129</t>
+        </is>
+      </c>
+      <c r="B130" s="13" t="inlineStr">
         <is>
           <t>11 Data Quality</t>
         </is>
       </c>
-      <c r="C126" s="14" t="inlineStr">
+      <c r="C130" s="14" t="inlineStr">
         <is>
           <t>Fan Out Alert</t>
         </is>
       </c>
-      <c r="D126" s="15" t="inlineStr">
+      <c r="D130" s="15" t="inlineStr">
         <is>
           <t>Keep this on the canvas. It catches the one failure mode the bridge architecture exists to prevent.</t>
         </is>
       </c>
-      <c r="E126" s="16" t="inlineStr">
+      <c r="E130" s="16" t="inlineStr">
         <is>
           <t>IF(
     [Invoiced MT] &gt; [Ordered MT] * 1.05,
@@ -6928,45 +7120,45 @@
 )</t>
         </is>
       </c>
-      <c r="F126" s="13" t="inlineStr">
+      <c r="F130" s="13" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G126" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H126" s="13" t="inlineStr">
+      <c r="G130" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H130" s="13" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I126" s="18" t="inlineStr">
+      <c r="I130" s="18" t="inlineStr">
         <is>
           <t>Model OK</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="50" customHeight="1">
-      <c r="A127" s="19" t="inlineStr">
-        <is>
-          <t>K-126</t>
-        </is>
-      </c>
-      <c r="B127" s="20" t="inlineStr">
+    <row r="131" ht="50" customHeight="1">
+      <c r="A131" s="19" t="inlineStr">
+        <is>
+          <t>K-130</t>
+        </is>
+      </c>
+      <c r="B131" s="20" t="inlineStr">
         <is>
           <t>11 Data Quality</t>
         </is>
       </c>
-      <c r="C127" s="21" t="inlineStr">
+      <c r="C131" s="21" t="inlineStr">
         <is>
           <t>Orphan Shipment Rows</t>
         </is>
       </c>
-      <c r="D127" s="22" t="inlineStr"/>
-      <c r="E127" s="23" t="inlineStr">
+      <c r="D131" s="22" t="inlineStr"/>
+      <c r="E131" s="23" t="inlineStr">
         <is>
           <t>CALCULATE(
     COUNTROWS(fact_Shipment),
@@ -6974,45 +7166,45 @@
 )</t>
         </is>
       </c>
-      <c r="F127" s="20" t="inlineStr">
+      <c r="F131" s="20" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G127" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H127" s="20" t="inlineStr">
+      <c r="G131" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H131" s="20" t="inlineStr">
         <is>
           <t>#,0</t>
         </is>
       </c>
-      <c r="I127" s="25" t="inlineStr">
+      <c r="I131" s="25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="50" customHeight="1">
-      <c r="A128" s="12" t="inlineStr">
-        <is>
-          <t>K-127</t>
-        </is>
-      </c>
-      <c r="B128" s="13" t="inlineStr">
+    <row r="132" ht="50" customHeight="1">
+      <c r="A132" s="12" t="inlineStr">
+        <is>
+          <t>K-131</t>
+        </is>
+      </c>
+      <c r="B132" s="13" t="inlineStr">
         <is>
           <t>11 Data Quality</t>
         </is>
       </c>
-      <c r="C128" s="14" t="inlineStr">
+      <c r="C132" s="14" t="inlineStr">
         <is>
           <t>Missing Promise Date %</t>
         </is>
       </c>
-      <c r="D128" s="15" t="inlineStr"/>
-      <c r="E128" s="16" t="inlineStr">
+      <c r="D132" s="15" t="inlineStr"/>
+      <c r="E132" s="16" t="inlineStr">
         <is>
           <t>DIVIDE(
     CALCULATE([Order Lines], ISBLANK(dim_SalesOrderLine[Promise_Date])),
@@ -7020,135 +7212,135 @@
 )</t>
         </is>
       </c>
-      <c r="F128" s="13" t="inlineStr">
+      <c r="F132" s="13" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G128" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H128" s="13" t="inlineStr">
+      <c r="G132" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H132" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I128" s="18" t="inlineStr">
+      <c r="I132" s="18" t="inlineStr">
         <is>
           <t>5.5%</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="26" customHeight="1">
-      <c r="A129" s="19" t="inlineStr">
-        <is>
-          <t>K-128</t>
-        </is>
-      </c>
-      <c r="B129" s="20" t="inlineStr">
+    <row r="133" ht="26" customHeight="1">
+      <c r="A133" s="19" t="inlineStr">
+        <is>
+          <t>K-132</t>
+        </is>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
         <is>
           <t>11 Data Quality</t>
         </is>
       </c>
-      <c r="C129" s="21" t="inlineStr">
+      <c r="C133" s="21" t="inlineStr">
         <is>
           <t>Sentinel Date Lines</t>
         </is>
       </c>
-      <c r="D129" s="22" t="inlineStr">
+      <c r="D133" s="22" t="inlineStr">
         <is>
           <t>Should read zero once the date cap is applied.</t>
         </is>
       </c>
-      <c r="E129" s="23" t="inlineStr">
+      <c r="E133" s="23" t="inlineStr">
         <is>
           <t>CALCULATE([Order Lines], dim_SalesOrderLine[Schedule_Ship_Date] &gt; DATE(2030,12,30))</t>
         </is>
       </c>
-      <c r="F129" s="20" t="inlineStr">
+      <c r="F133" s="20" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G129" s="24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H129" s="20" t="inlineStr">
+      <c r="G133" s="24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H133" s="20" t="inlineStr">
         <is>
           <t>#,0</t>
         </is>
       </c>
-      <c r="I129" s="25" t="inlineStr">
+      <c r="I133" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="26" customHeight="1">
-      <c r="A130" s="12" t="inlineStr">
-        <is>
-          <t>K-129</t>
-        </is>
-      </c>
-      <c r="B130" s="13" t="inlineStr">
+    <row r="134" ht="26" customHeight="1">
+      <c r="A134" s="12" t="inlineStr">
+        <is>
+          <t>K-133</t>
+        </is>
+      </c>
+      <c r="B134" s="13" t="inlineStr">
         <is>
           <t>11 Data Quality</t>
         </is>
       </c>
-      <c r="C130" s="14" t="inlineStr">
+      <c r="C134" s="14" t="inlineStr">
         <is>
           <t>Unknown Currency Lines</t>
         </is>
       </c>
-      <c r="D130" s="15" t="inlineStr"/>
-      <c r="E130" s="16" t="inlineStr">
+      <c r="D134" s="15" t="inlineStr"/>
+      <c r="E134" s="16" t="inlineStr">
         <is>
           <t>CALCULATE([Order Lines], dim_Currency[Currency_Code] = "UNK")</t>
         </is>
       </c>
-      <c r="F130" s="13" t="inlineStr">
+      <c r="F134" s="13" t="inlineStr">
         <is>
           <t>multiple</t>
         </is>
       </c>
-      <c r="G130" s="17" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="H130" s="13" t="inlineStr">
+      <c r="G134" s="17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="H134" s="13" t="inlineStr">
         <is>
           <t>#,0</t>
         </is>
       </c>
-      <c r="I130" s="18" t="inlineStr">
+      <c r="I134" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="50" customHeight="1">
-      <c r="A131" s="19" t="inlineStr">
-        <is>
-          <t>K-130</t>
-        </is>
-      </c>
-      <c r="B131" s="20" t="inlineStr">
+    <row r="135" ht="50" customHeight="1">
+      <c r="A135" s="19" t="inlineStr">
+        <is>
+          <t>K-134</t>
+        </is>
+      </c>
+      <c r="B135" s="20" t="inlineStr">
         <is>
           <t>12 Report Helpers</t>
         </is>
       </c>
-      <c r="C131" s="21" t="inlineStr">
+      <c r="C135" s="21" t="inlineStr">
         <is>
           <t>Selected Period Label</t>
         </is>
       </c>
-      <c r="D131" s="22" t="inlineStr"/>
-      <c r="E131" s="23" t="inlineStr">
+      <c r="D135" s="22" t="inlineStr"/>
+      <c r="E135" s="23" t="inlineStr">
         <is>
           <t>VAR MinD = MIN(dim_Date[Date])
 VAR MaxD = MAX(dim_Date[Date])
@@ -7156,45 +7348,45 @@
     FORMAT(MinD, "d mmm yyyy") &amp; "  to  " &amp; FORMAT(MaxD, "d mmm yyyy")</t>
         </is>
       </c>
-      <c r="F131" s="20" t="inlineStr">
+      <c r="F135" s="20" t="inlineStr">
         <is>
           <t>dim_Date</t>
         </is>
       </c>
-      <c r="G131" s="27" t="inlineStr">
+      <c r="G135" s="27" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H131" s="20" t="inlineStr">
+      <c r="H135" s="20" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I131" s="25" t="inlineStr">
+      <c r="I135" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60.5" customHeight="1">
-      <c r="A132" s="12" t="inlineStr">
-        <is>
-          <t>K-131</t>
-        </is>
-      </c>
-      <c r="B132" s="13" t="inlineStr">
+    <row r="136" ht="60.5" customHeight="1">
+      <c r="A136" s="12" t="inlineStr">
+        <is>
+          <t>K-135</t>
+        </is>
+      </c>
+      <c r="B136" s="13" t="inlineStr">
         <is>
           <t>12 Report Helpers</t>
         </is>
       </c>
-      <c r="C132" s="14" t="inlineStr">
+      <c r="C136" s="14" t="inlineStr">
         <is>
           <t>Partial Month Warning</t>
         </is>
       </c>
-      <c r="D132" s="15" t="inlineStr"/>
-      <c r="E132" s="16" t="inlineStr">
+      <c r="D136" s="15" t="inlineStr"/>
+      <c r="E136" s="16" t="inlineStr">
         <is>
           <t>IF(
     SELECTEDVALUE(dim_Date[Is_Complete_Month]) = FALSE(),
@@ -7203,29 +7395,29 @@
 )</t>
         </is>
       </c>
-      <c r="F132" s="13" t="inlineStr">
+      <c r="F136" s="13" t="inlineStr">
         <is>
           <t>dim_Date</t>
         </is>
       </c>
-      <c r="G132" s="26" t="inlineStr">
+      <c r="G136" s="26" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H132" s="13" t="inlineStr">
+      <c r="H136" s="13" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="I132" s="18" t="inlineStr">
+      <c r="I136" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I132"/>
+  <autoFilter ref="A1:I136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -7237,7 +7429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7293,12 +7485,12 @@
       </c>
       <c r="C2" s="29" t="inlineStr">
         <is>
-          <t>RESOLVED - USC conversion</t>
+          <t>RESOLVED - USC and full FX coverage</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>d_exchange_rate resolves USC (Dolar Compra) as 1:1 with USD. All 2,960 lines now convert.</t>
+          <t>d_exchange_rate resolves USC as 1:1 with USD, and the v2 query supplies Exchange_Rate directly. Coverage is 100.000%.</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
@@ -7315,59 +7507,59 @@
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
         <is>
-          <t>BLK-01</t>
+          <t>BLK-00b</t>
         </is>
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>Revenue &amp; Commercial</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="C3" s="32" t="inlineStr">
         <is>
-          <t>Gross margin / contribution per tonne</t>
+          <t>RESOLVED - WHERE clause precedence</t>
         </is>
       </c>
       <c r="D3" s="22" t="inlineStr">
         <is>
-          <t>No cost data of any kind in the three facts — no COGS, standard cost or freight cost.</t>
+          <t>Fixed in the v2 sales order query. Cancelled lines went 39 to 0 and the extract grew to 68,977.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
         <is>
-          <t>Add a cost fact at item x plant x month. Standard cost alone unlocks the whole margin family.</t>
+          <t>Apply the same brackets to the invoice and shipment queries.</t>
         </is>
       </c>
       <c r="F3" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="28" t="inlineStr">
         <is>
-          <t>BLK-02</t>
+          <t>BLK-01</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Revenue &amp; Commercial</t>
         </is>
       </c>
       <c r="C4" s="29" t="inlineStr">
         <is>
-          <t>DSO, overdue balances, cash collection</t>
+          <t>Gross margin / contribution per tonne</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>No payment or settlement records. Term_Name gives the agreed term but nothing confirms collection.</t>
+          <t>No cost data of any kind in the three facts — no COGS, standard cost or freight cost.</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>Requires an AR ledger or payments fact keyed on invoice.</t>
+          <t>Add a cost fact at item x plant x month. Standard cost alone unlocks the whole margin family.</t>
         </is>
       </c>
       <c r="F4" s="34" t="inlineStr">
@@ -7379,30 +7571,30 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>BLK-03</t>
+          <t>BLK-02</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>Freight cost per tonne / cost per lane</t>
+          <t>DSO, overdue balances, cash collection</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>No freight rate or carrier cost columns anywhere in f_Shipment.</t>
+          <t>No payment or settlement records. Term_Name gives the agreed term but nothing confirms collection.</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>Join freight invoices or a rate card on carrier x lane.</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="inlineStr">
+          <t>Requires an AR ledger or payments fact keyed on invoice.</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7411,27 +7603,27 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="28" t="inlineStr">
         <is>
-          <t>BLK-04</t>
+          <t>BLK-03</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="C6" s="29" t="inlineStr">
         <is>
-          <t>Actual transit time door to door</t>
+          <t>Freight cost per tonne / cost per lane</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>Trip stop actual arrival and actual departure carry identical timestamps — computed transit is 0.00 days across 63,969 rows.</t>
+          <t>No freight rate or carrier cost columns anywhere in f_Shipment.</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>Needs genuine event capture at pickup and drop-off. Use delay-against-plan as the proxy meanwhile.</t>
+          <t>Join freight invoices or a rate card on carrier x lane.</t>
         </is>
       </c>
       <c r="F6" s="34" t="inlineStr">
@@ -7443,30 +7635,30 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>BLK-05</t>
+          <t>BLK-04</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Returns</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>Link a credit back to the original sale</t>
+          <t>Actual transit time door to door</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>Line_DFF_Quick_RMA_Original_Line_Id is populated on 8 rows and none of the 8 resolve to any Line_Id.</t>
+          <t>Trip stop actual arrival and actual departure carry identical timestamps — computed transit is 0.00 days across 63,969 rows.</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>Source-side fix. Without it credit root-cause cannot reach the original transaction.</t>
-        </is>
-      </c>
-      <c r="F7" s="33" t="inlineStr">
+          <t>Needs genuine event capture at pickup and drop-off. Use delay-against-plan as the proxy meanwhile.</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7475,27 +7667,27 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
-          <t>BLK-06</t>
+          <t>BLK-05</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Returns</t>
         </is>
       </c>
       <c r="C8" s="29" t="inlineStr">
         <is>
-          <t>Year-on-year growth</t>
+          <t>Link a credit back to the original sale</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>The extract starts January 2026. 99.7% of invoice rows are 2026.</t>
+          <t>Line_DFF_Quick_RMA_Original_Line_Id is populated on 8 rows and none of the 8 resolve to any Line_Id.</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>Extend the source query window. The model already supports it.</t>
+          <t>Source-side fix. Without it credit root-cause cannot reach the original transaction.</t>
         </is>
       </c>
       <c r="F8" s="34" t="inlineStr">
@@ -7507,39 +7699,39 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>BLK-08</t>
+          <t>BLK-06</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>Vessel / voyage reliability</t>
+          <t>Year-on-year growth</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>Voyage columns are 0.1-0.4% populated (117 to 337 rows of 84,505).</t>
+          <t>The extract starts January 2026. 99.7% of invoice rows are 2026.</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>Backfill voyage data, or scope the metric to ocean shipments only.</t>
+          <t>Extend the source query window. The model already supports it.</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="28" t="inlineStr">
         <is>
-          <t>BLK-09</t>
+          <t>BLK-08</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -7549,17 +7741,17 @@
       </c>
       <c r="C10" s="29" t="inlineStr">
         <is>
-          <t>Container utilisation / fill rate</t>
+          <t>Vessel / voyage reliability</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Delivery_Detail_LPN_Container_Name is 3.6% populated; Trip_DFF_Container_Number is 0%.</t>
+          <t>Voyage columns are 0.1-0.4% populated (117 to 337 rows of 84,505).</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Capture container assignment on every containerised delivery.</t>
+          <t>Backfill voyage data, or scope the metric to ocean shipments only.</t>
         </is>
       </c>
       <c r="F10" s="36" t="inlineStr">
@@ -7571,133 +7763,165 @@
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>BLK-10</t>
+          <t>BLK-09</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>Delivered and received volume</t>
+          <t>Container utilisation / fill rate</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>Delivered_Qty_MT, Received_Qty_MT and Scheduled_Qty_MT are populated but every value is zero across all 84,505 clean rows.</t>
+          <t>Delivery_Detail_LPN_Container_Name is 3.6% populated; Trip_DFF_Container_Number is 0%.</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>Ask whether delivery confirmation is captured at all. If it is, the ETL is not carrying it.</t>
-        </is>
-      </c>
-      <c r="F11" s="33" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Capture container assignment on every containerised delivery.</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="28" t="inlineStr">
         <is>
-          <t>BLK-11</t>
+          <t>BLK-10</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C12" s="29" t="inlineStr">
         <is>
-          <t>Product family / grade hierarchy</t>
+          <t>Delivered and received volume</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Product data is masked in this sample and no hierarchy columns are visible.</t>
+          <t>Delivered_Qty_MT, Received_Qty_MT and Scheduled_Qty_MT are populated but every value is zero across all 84,505 clean rows.</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>Re-profile on unmasked data — the hierarchy may already exist.</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Ask whether delivery confirmation is captured at all. If it is, the ETL is not carrying it.</t>
+        </is>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>BLK-12</t>
+          <t>BLK-11</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>FX impact split from price and volume</t>
+          <t>Product family / grade hierarchy</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>Now buildable - dim_ExchangeRate supplies daily Corporate rates. Not yet in the measure set.</t>
+          <t>Product data is masked in this sample and no hierarchy columns are visible.</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>Add a price/volume/FX bridge measure group. No data gap remains.</t>
+          <t>Re-profile on unmasked data — the hierarchy may already exist.</t>
         </is>
       </c>
       <c r="F13" s="37" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="28" t="inlineStr">
         <is>
+          <t>BLK-12</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>FX impact split from price and volume</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Now buildable - dim_ExchangeRate supplies daily Corporate rates. Not yet in the measure set.</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Add a price/volume/FX bridge measure group. No data gap remains.</t>
+        </is>
+      </c>
+      <c r="F14" s="38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
           <t>BLK-13</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Forecasting</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>Forecast accuracy / plan vs actual</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>No forecast or budget data in scope.</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>Add a forecast fact at customer x product x month.</t>
         </is>
       </c>
-      <c r="F14" s="36" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
